--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\La Melitaa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42252B50-9299-467E-99C2-51909026F68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362AA545-8CD4-4394-9386-E222564E3622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEBFA179-F109-4830-AF10-F3EF48EB9847}"/>
   </bookViews>
@@ -590,7 +590,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="6">
-        <v>46245.008333333331</v>
+        <v>46245.045138888891</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>9</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\La Melitaa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\La Melitaa - shuvrotai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3207E3B1-E493-40C7-BF79-AAA6D2B535AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB860B5-B2BB-4CF9-A367-C65F8B00B5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEBFA179-F109-4830-AF10-F3EF48EB9847}"/>
   </bookViews>
@@ -38,30 +38,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1851" uniqueCount="725">
   <si>
     <t>ID</t>
   </si>
@@ -1267,6 +1245,975 @@
   </si>
   <si>
     <t>Happy New Year #lamelitaaa #imagechallenge #viralphoto #fbphotos</t>
+  </si>
+  <si>
+    <t>26-08-2026 03:05</t>
+  </si>
+  <si>
+    <t>26-08-2026 06:05</t>
+  </si>
+  <si>
+    <t>26-08-2026 08:35</t>
+  </si>
+  <si>
+    <t>26-08-2026 11:35</t>
+  </si>
+  <si>
+    <t>26-08-2026 17:35</t>
+  </si>
+  <si>
+    <t>26-08-2026 19:05</t>
+  </si>
+  <si>
+    <t>26-08-2026 21:05</t>
+  </si>
+  <si>
+    <t>27-08-2026 03:05</t>
+  </si>
+  <si>
+    <t>27-08-2026 08:35</t>
+  </si>
+  <si>
+    <t>27-08-2026 11:35</t>
+  </si>
+  <si>
+    <t>27-08-2026 17:35</t>
+  </si>
+  <si>
+    <t>27-08-2026 19:05</t>
+  </si>
+  <si>
+    <t>27-08-2026 21:05</t>
+  </si>
+  <si>
+    <t>28-08-2026 06:05</t>
+  </si>
+  <si>
+    <t>28-08-2026 08:35</t>
+  </si>
+  <si>
+    <t>28-08-2026 11:35</t>
+  </si>
+  <si>
+    <t>28-08-2026 17:35</t>
+  </si>
+  <si>
+    <t>28-08-2026 19:05</t>
+  </si>
+  <si>
+    <t>28-08-2026 21:05</t>
+  </si>
+  <si>
+    <t>29-08-2026 03:05</t>
+  </si>
+  <si>
+    <t>29-08-2026 08:35</t>
+  </si>
+  <si>
+    <t>29-08-2026 11:35</t>
+  </si>
+  <si>
+    <t>29-08-2026 17:35</t>
+  </si>
+  <si>
+    <t>29-08-2026 19:05</t>
+  </si>
+  <si>
+    <t>29-08-2026 21:05</t>
+  </si>
+  <si>
+    <t>30-08-2026 03:05</t>
+  </si>
+  <si>
+    <t>30-08-2026 06:05</t>
+  </si>
+  <si>
+    <t>30-08-2026 08:35</t>
+  </si>
+  <si>
+    <t>30-08-2026 11:35</t>
+  </si>
+  <si>
+    <t>30-08-2026 17:35</t>
+  </si>
+  <si>
+    <t>30-08-2026 19:05</t>
+  </si>
+  <si>
+    <t>30-08-2026 21:05</t>
+  </si>
+  <si>
+    <t>31-08-2026 03:05</t>
+  </si>
+  <si>
+    <t>31-08-2026 06:05</t>
+  </si>
+  <si>
+    <t>31-08-2026 08:35</t>
+  </si>
+  <si>
+    <t>31-08-2026 11:35</t>
+  </si>
+  <si>
+    <t>31-08-2026 17:35</t>
+  </si>
+  <si>
+    <t>31-08-2026 19:05</t>
+  </si>
+  <si>
+    <t>31-08-2026 21:05</t>
+  </si>
+  <si>
+    <t>01-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>01-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>01-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>01-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>01-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>01-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>01-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>02-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>02-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>02-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>02-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>02-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>02-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>02-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>03-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>03-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>03-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>03-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>03-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>03-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>03-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>04-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>04-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>04-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>04-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>04-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>04-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>05-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>05-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>05-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>05-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>05-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>05-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>05-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>06-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>06-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>06-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>06-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>06-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>06-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>06-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>07-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>07-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>07-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>07-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>07-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>07-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>07-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>08-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>08-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>08-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>08-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>08-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>08-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>08-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>09-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>09-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>09-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>09-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>09-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>09-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>09-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>10-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>10-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>10-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>10-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>10-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>10-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>10-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>11-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>11-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>11-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>11-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>11-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>11-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>11-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>12-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>12-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>12-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>12-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>12-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>12-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>12-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>13-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>13-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>13-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>13-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>13-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>13-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>13-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>14-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>14-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>14-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>14-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>14-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>14-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>14-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>15-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>15-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>15-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>15-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>15-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>15-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>15-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>16-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>16-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>16-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>16-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>16-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>16-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>16-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>17-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>17-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>17-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>17-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>17-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>17-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>17-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>18-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>18-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>18-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>18-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>18-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>18-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>18-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>19-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>19-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>19-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>19-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>19-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>19-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>19-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>20-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>20-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>20-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>20-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>20-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>20-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>20-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>21-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>21-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>21-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>21-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>21-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>21-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>21-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>22-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>22-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>22-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>22-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>22-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>22-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>22-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>23-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>23-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>23-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>23-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>23-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>23-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>23-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>24-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>24-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>24-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>24-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>24-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>24-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>24-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>25-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>25-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>25-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>25-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>25-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>25-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>25-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>26-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>26-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>26-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>26-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>26-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>26-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>26-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>27-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>27-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>27-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>27-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>27-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>27-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>27-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>28-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>28-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>28-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>28-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>28-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>28-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>28-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>29-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>29-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>29-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>29-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>29-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>29-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>29-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>30-09-2026 03:05</t>
+  </si>
+  <si>
+    <t>30-09-2026 06:05</t>
+  </si>
+  <si>
+    <t>30-09-2026 08:35</t>
+  </si>
+  <si>
+    <t>30-09-2026 11:35</t>
+  </si>
+  <si>
+    <t>30-09-2026 17:35</t>
+  </si>
+  <si>
+    <t>30-09-2026 19:05</t>
+  </si>
+  <si>
+    <t>30-09-2026 21:05</t>
+  </si>
+  <si>
+    <t>01-10-2026 03:05</t>
+  </si>
+  <si>
+    <t>01-10-2026 06:05</t>
+  </si>
+  <si>
+    <t>01-10-2026 08:35</t>
+  </si>
+  <si>
+    <t>01-10-2026 11:35</t>
+  </si>
+  <si>
+    <t>01-10-2026 17:35</t>
+  </si>
+  <si>
+    <t>01-10-2026 19:05</t>
+  </si>
+  <si>
+    <t>01-10-2026 21:05</t>
+  </si>
+  <si>
+    <t>02-10-2026 03:05</t>
+  </si>
+  <si>
+    <t>02-10-2026 06:05</t>
+  </si>
+  <si>
+    <t>02-10-2026 08:35</t>
+  </si>
+  <si>
+    <t>02-10-2026 11:35</t>
+  </si>
+  <si>
+    <t>02-10-2026 17:35</t>
+  </si>
+  <si>
+    <t>02-10-2026 19:05</t>
+  </si>
+  <si>
+    <t>02-10-2026 21:05</t>
+  </si>
+  <si>
+    <t>03-10-2026 03:05</t>
+  </si>
+  <si>
+    <t>03-10-2026 06:05</t>
+  </si>
+  <si>
+    <t>03-10-2026 08:35</t>
+  </si>
+  <si>
+    <t>03-10-2026 11:35</t>
+  </si>
+  <si>
+    <t>03-10-2026 17:35</t>
+  </si>
+  <si>
+    <t>03-10-2026 19:05</t>
+  </si>
+  <si>
+    <t>03-10-2026 21:05</t>
+  </si>
+  <si>
+    <t>04-10-2026 03:05</t>
+  </si>
+  <si>
+    <t>04-10-2026 06:05</t>
+  </si>
+  <si>
+    <t>04-10-2026 08:35</t>
+  </si>
+  <si>
+    <t>04-10-2026 11:35</t>
+  </si>
+  <si>
+    <t>04-10-2026 17:35</t>
+  </si>
+  <si>
+    <t>04-10-2026 19:05</t>
+  </si>
+  <si>
+    <t>04-10-2026 21:05</t>
+  </si>
+  <si>
+    <t>05-10-2026 03:05</t>
+  </si>
+  <si>
+    <t>05-10-2026 06:05</t>
+  </si>
+  <si>
+    <t>05-10-2026 08:35</t>
+  </si>
+  <si>
+    <t>05-10-2026 11:35</t>
+  </si>
+  <si>
+    <t>05-10-2026 17:35</t>
+  </si>
+  <si>
+    <t>05-10-2026 19:05</t>
+  </si>
+  <si>
+    <t>05-10-2026 21:05</t>
+  </si>
+  <si>
+    <t>06-10-2026 03:05</t>
+  </si>
+  <si>
+    <t>06-10-2026 06:05</t>
+  </si>
+  <si>
+    <t>06-10-2026 08:35</t>
+  </si>
+  <si>
+    <t>06-10-2026 11:35</t>
+  </si>
+  <si>
+    <t>06-10-2026 17:35</t>
+  </si>
+  <si>
+    <t>06-10-2026 19:05</t>
+  </si>
+  <si>
+    <t>06-10-2026 21:05</t>
+  </si>
+  <si>
+    <t>07-10-2026 03:05</t>
+  </si>
+  <si>
+    <t>07-10-2026 06:05</t>
+  </si>
+  <si>
+    <t>07-10-2026 08:35</t>
+  </si>
+  <si>
+    <t>07-10-2026 11:35</t>
+  </si>
+  <si>
+    <t>07-10-2026 17:35</t>
+  </si>
+  <si>
+    <t>07-10-2026 19:05</t>
+  </si>
+  <si>
+    <t>07-10-2026 21:05</t>
+  </si>
+  <si>
+    <t>08-10-2026 03:05</t>
+  </si>
+  <si>
+    <t>08-10-2026 06:05</t>
+  </si>
+  <si>
+    <t>08-10-2026 08:35</t>
+  </si>
+  <si>
+    <t>08-10-2026 11:35</t>
+  </si>
+  <si>
+    <t>08-10-2026 17:35</t>
+  </si>
+  <si>
+    <t>08-10-2026 19:05</t>
+  </si>
+  <si>
+    <t>08-10-2026 21:05</t>
+  </si>
+  <si>
+    <t>09-10-2026 03:05</t>
+  </si>
+  <si>
+    <t>09-10-2026 06:05</t>
+  </si>
+  <si>
+    <t>09-10-2026 08:35</t>
+  </si>
+  <si>
+    <t>09-10-2026 11:35</t>
+  </si>
+  <si>
+    <t>09-10-2026 17:35</t>
+  </si>
+  <si>
+    <t>09-10-2026 19:05</t>
+  </si>
+  <si>
+    <t>09-10-2026 21:05</t>
+  </si>
+  <si>
+    <t>10-10-2026 03:05</t>
+  </si>
+  <si>
+    <t>10-10-2026 06:05</t>
+  </si>
+  <si>
+    <t>10-10-2026 08:35</t>
+  </si>
+  <si>
+    <t>10-10-2026 11:35</t>
+  </si>
+  <si>
+    <t>10-10-2026 17:35</t>
+  </si>
+  <si>
+    <t>10-10-2026 19:05</t>
+  </si>
+  <si>
+    <t>10-10-2026 21:05</t>
+  </si>
+  <si>
+    <t>11-10-2026 03:05</t>
+  </si>
+  <si>
+    <t>11-10-2026 06:05</t>
+  </si>
+  <si>
+    <t>11-10-2026 08:35</t>
+  </si>
+  <si>
+    <t>11-10-2026 11:35</t>
+  </si>
+  <si>
+    <t>11-10-2026 17:35</t>
   </si>
 </sst>
 </file>
@@ -1906,9 +2853,8 @@
       <c r="D9" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="6" t="str" cm="1">
-        <f t="array" ref="E9">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-08-2026 03:05</v>
+      <c r="E9" s="6" t="s">
+        <v>402</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>8</v>
@@ -1924,9 +2870,8 @@
       <c r="D10" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="6" t="str" cm="1">
-        <f t="array" ref="E10">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-08-2026 06:05</v>
+      <c r="E10" s="6" t="s">
+        <v>403</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>8</v>
@@ -1942,9 +2887,8 @@
       <c r="D11" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="6" t="str" cm="1">
-        <f t="array" ref="E11">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-08-2026 08:35</v>
+      <c r="E11" s="6" t="s">
+        <v>404</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>8</v>
@@ -1960,9 +2904,8 @@
       <c r="D12" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="6" t="str" cm="1">
-        <f t="array" ref="E12">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-08-2026 11:35</v>
+      <c r="E12" s="6" t="s">
+        <v>405</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>8</v>
@@ -1978,9 +2921,8 @@
       <c r="D13" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="6" t="str" cm="1">
-        <f t="array" ref="E13">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-08-2026 17:35</v>
+      <c r="E13" s="6" t="s">
+        <v>406</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>8</v>
@@ -1996,9 +2938,8 @@
       <c r="D14" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="6" t="str" cm="1">
-        <f t="array" ref="E14">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-08-2026 19:05</v>
+      <c r="E14" s="6" t="s">
+        <v>407</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>8</v>
@@ -2014,9 +2955,8 @@
       <c r="D15" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="6" t="str" cm="1">
-        <f t="array" ref="E15">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-08-2026 21:05</v>
+      <c r="E15" s="6" t="s">
+        <v>408</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>8</v>
@@ -2032,9 +2972,8 @@
       <c r="D16" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="6" t="str" cm="1">
-        <f t="array" ref="E16">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-08-2026 03:05</v>
+      <c r="E16" s="6" t="s">
+        <v>409</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>8</v>
@@ -2050,9 +2989,8 @@
       <c r="D17" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="6" t="str" cm="1">
-        <f t="array" ref="E17">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-08-2026 06:05</v>
+      <c r="E17" s="6">
+        <v>46261.253472222219</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>8</v>
@@ -2068,9 +3006,8 @@
       <c r="D18" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="6" t="str" cm="1">
-        <f t="array" ref="E18">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-08-2026 08:35</v>
+      <c r="E18" s="6" t="s">
+        <v>410</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>8</v>
@@ -2086,9 +3023,8 @@
       <c r="D19" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="6" t="str" cm="1">
-        <f t="array" ref="E19">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-08-2026 11:35</v>
+      <c r="E19" s="6" t="s">
+        <v>411</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>8</v>
@@ -2104,9 +3040,8 @@
       <c r="D20" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="6" t="str" cm="1">
-        <f t="array" ref="E20">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-08-2026 17:35</v>
+      <c r="E20" s="6" t="s">
+        <v>412</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>8</v>
@@ -2122,9 +3057,8 @@
       <c r="D21" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="6" t="str" cm="1">
-        <f t="array" ref="E21">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-08-2026 19:05</v>
+      <c r="E21" s="6" t="s">
+        <v>413</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>8</v>
@@ -2140,9 +3074,8 @@
       <c r="D22" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="6" t="str" cm="1">
-        <f t="array" ref="E22">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-08-2026 21:05</v>
+      <c r="E22" s="6" t="s">
+        <v>414</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>8</v>
@@ -2158,9 +3091,8 @@
       <c r="D23" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="6" t="str" cm="1">
-        <f t="array" ref="E23">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-08-2026 03:05</v>
+      <c r="E23" s="6">
+        <v>46262.128472222219</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>8</v>
@@ -2176,9 +3108,8 @@
       <c r="D24" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="6" t="str" cm="1">
-        <f t="array" ref="E24">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-08-2026 06:05</v>
+      <c r="E24" s="6" t="s">
+        <v>415</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>8</v>
@@ -2194,9 +3125,8 @@
       <c r="D25" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="6" t="str" cm="1">
-        <f t="array" ref="E25">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-08-2026 08:35</v>
+      <c r="E25" s="6" t="s">
+        <v>416</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>8</v>
@@ -2212,9 +3142,8 @@
       <c r="D26" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="6" t="str" cm="1">
-        <f t="array" ref="E26">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-08-2026 11:35</v>
+      <c r="E26" s="6" t="s">
+        <v>417</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>8</v>
@@ -2230,9 +3159,8 @@
       <c r="D27" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="6" t="str" cm="1">
-        <f t="array" ref="E27">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-08-2026 17:35</v>
+      <c r="E27" s="6" t="s">
+        <v>418</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>8</v>
@@ -2248,9 +3176,8 @@
       <c r="D28" t="s">
         <v>70</v>
       </c>
-      <c r="E28" s="6" t="str" cm="1">
-        <f t="array" ref="E28">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-08-2026 19:05</v>
+      <c r="E28" s="6" t="s">
+        <v>419</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>8</v>
@@ -2266,9 +3193,8 @@
       <c r="D29" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="6" t="str" cm="1">
-        <f t="array" ref="E29">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-08-2026 21:05</v>
+      <c r="E29" s="6" t="s">
+        <v>420</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>8</v>
@@ -2284,9 +3210,8 @@
       <c r="D30" t="s">
         <v>70</v>
       </c>
-      <c r="E30" s="6" t="str" cm="1">
-        <f t="array" ref="E30">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-08-2026 03:05</v>
+      <c r="E30" s="6" t="s">
+        <v>421</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>8</v>
@@ -2302,9 +3227,8 @@
       <c r="D31" t="s">
         <v>70</v>
       </c>
-      <c r="E31" s="6" t="str" cm="1">
-        <f t="array" ref="E31">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-08-2026 06:05</v>
+      <c r="E31" s="6">
+        <v>46263.253472222219</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>8</v>
@@ -2320,9 +3244,8 @@
       <c r="D32" t="s">
         <v>70</v>
       </c>
-      <c r="E32" s="6" t="str" cm="1">
-        <f t="array" ref="E32">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-08-2026 08:35</v>
+      <c r="E32" s="6" t="s">
+        <v>422</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>8</v>
@@ -2338,9 +3261,8 @@
       <c r="D33" t="s">
         <v>70</v>
       </c>
-      <c r="E33" s="6" t="str" cm="1">
-        <f t="array" ref="E33">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-08-2026 11:35</v>
+      <c r="E33" s="6" t="s">
+        <v>423</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>8</v>
@@ -2356,9 +3278,8 @@
       <c r="D34" t="s">
         <v>70</v>
       </c>
-      <c r="E34" s="6" t="str" cm="1">
-        <f t="array" ref="E34">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-08-2026 17:35</v>
+      <c r="E34" s="6" t="s">
+        <v>424</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>8</v>
@@ -2374,9 +3295,8 @@
       <c r="D35" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="6" t="str" cm="1">
-        <f t="array" ref="E35">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-08-2026 19:05</v>
+      <c r="E35" s="6" t="s">
+        <v>425</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>8</v>
@@ -2392,9 +3312,8 @@
       <c r="D36" t="s">
         <v>70</v>
       </c>
-      <c r="E36" s="6" t="str" cm="1">
-        <f t="array" ref="E36">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-08-2026 21:05</v>
+      <c r="E36" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>8</v>
@@ -2410,9 +3329,8 @@
       <c r="D37" t="s">
         <v>70</v>
       </c>
-      <c r="E37" s="6" t="str" cm="1">
-        <f t="array" ref="E37">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-08-2026 03:05</v>
+      <c r="E37" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>8</v>
@@ -2428,9 +3346,8 @@
       <c r="D38" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="6" t="str" cm="1">
-        <f t="array" ref="E38">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-08-2026 06:05</v>
+      <c r="E38" s="6" t="s">
+        <v>428</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>8</v>
@@ -2446,9 +3363,8 @@
       <c r="D39" t="s">
         <v>70</v>
       </c>
-      <c r="E39" s="6" t="str" cm="1">
-        <f t="array" ref="E39">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-08-2026 08:35</v>
+      <c r="E39" s="6" t="s">
+        <v>429</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>8</v>
@@ -2464,9 +3380,8 @@
       <c r="D40" t="s">
         <v>70</v>
       </c>
-      <c r="E40" s="6" t="str" cm="1">
-        <f t="array" ref="E40">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-08-2026 11:35</v>
+      <c r="E40" s="6" t="s">
+        <v>430</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>8</v>
@@ -2482,9 +3397,8 @@
       <c r="D41" t="s">
         <v>71</v>
       </c>
-      <c r="E41" s="6" t="str" cm="1">
-        <f t="array" ref="E41">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-08-2026 17:35</v>
+      <c r="E41" s="6" t="s">
+        <v>431</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>8</v>
@@ -2500,9 +3414,8 @@
       <c r="D42" t="s">
         <v>71</v>
       </c>
-      <c r="E42" s="6" t="str" cm="1">
-        <f t="array" ref="E42">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-08-2026 19:05</v>
+      <c r="E42" s="6" t="s">
+        <v>432</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>8</v>
@@ -2518,9 +3431,8 @@
       <c r="D43" t="s">
         <v>71</v>
       </c>
-      <c r="E43" s="6" t="str" cm="1">
-        <f t="array" ref="E43">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-08-2026 21:05</v>
+      <c r="E43" s="6" t="s">
+        <v>433</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>8</v>
@@ -2536,9 +3448,8 @@
       <c r="D44" t="s">
         <v>71</v>
       </c>
-      <c r="E44" s="6" t="str" cm="1">
-        <f t="array" ref="E44">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>31-08-2026 03:05</v>
+      <c r="E44" s="6" t="s">
+        <v>434</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>8</v>
@@ -2554,9 +3465,8 @@
       <c r="D45" t="s">
         <v>71</v>
       </c>
-      <c r="E45" s="6" t="str" cm="1">
-        <f t="array" ref="E45">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>31-08-2026 06:05</v>
+      <c r="E45" s="6" t="s">
+        <v>435</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>8</v>
@@ -2572,9 +3482,8 @@
       <c r="D46" t="s">
         <v>71</v>
       </c>
-      <c r="E46" s="6" t="str" cm="1">
-        <f t="array" ref="E46">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>31-08-2026 08:35</v>
+      <c r="E46" s="6" t="s">
+        <v>436</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>8</v>
@@ -2590,9 +3499,8 @@
       <c r="D47" t="s">
         <v>71</v>
       </c>
-      <c r="E47" s="6" t="str" cm="1">
-        <f t="array" ref="E47">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>31-08-2026 11:35</v>
+      <c r="E47" s="6" t="s">
+        <v>437</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>8</v>
@@ -2608,9 +3516,8 @@
       <c r="D48" t="s">
         <v>71</v>
       </c>
-      <c r="E48" s="6" t="str" cm="1">
-        <f t="array" ref="E48">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>31-08-2026 17:35</v>
+      <c r="E48" s="6" t="s">
+        <v>438</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>8</v>
@@ -2626,9 +3533,8 @@
       <c r="D49" t="s">
         <v>71</v>
       </c>
-      <c r="E49" s="6" t="str" cm="1">
-        <f t="array" ref="E49">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>31-08-2026 19:05</v>
+      <c r="E49" s="6" t="s">
+        <v>439</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>8</v>
@@ -2644,9 +3550,8 @@
       <c r="D50" t="s">
         <v>71</v>
       </c>
-      <c r="E50" s="6" t="str" cm="1">
-        <f t="array" ref="E50">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>31-08-2026 21:05</v>
+      <c r="E50" s="6" t="s">
+        <v>440</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>8</v>
@@ -2662,9 +3567,8 @@
       <c r="D51" t="s">
         <v>71</v>
       </c>
-      <c r="E51" s="6" t="str" cm="1">
-        <f t="array" ref="E51">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-09-2026 03:05</v>
+      <c r="E51" s="6" t="s">
+        <v>441</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>8</v>
@@ -2680,9 +3584,8 @@
       <c r="D52" t="s">
         <v>71</v>
       </c>
-      <c r="E52" s="6" t="str" cm="1">
-        <f t="array" ref="E52">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-09-2026 06:05</v>
+      <c r="E52" s="6" t="s">
+        <v>442</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>8</v>
@@ -2698,9 +3601,8 @@
       <c r="D53" t="s">
         <v>71</v>
       </c>
-      <c r="E53" s="6" t="str" cm="1">
-        <f t="array" ref="E53">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-09-2026 08:35</v>
+      <c r="E53" s="6" t="s">
+        <v>443</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>8</v>
@@ -2716,9 +3618,8 @@
       <c r="D54" t="s">
         <v>71</v>
       </c>
-      <c r="E54" s="6" t="str" cm="1">
-        <f t="array" ref="E54">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-09-2026 11:35</v>
+      <c r="E54" s="6" t="s">
+        <v>444</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>8</v>
@@ -2734,9 +3635,8 @@
       <c r="D55" t="s">
         <v>71</v>
       </c>
-      <c r="E55" s="6" t="str" cm="1">
-        <f t="array" ref="E55">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-09-2026 17:35</v>
+      <c r="E55" s="6" t="s">
+        <v>445</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>8</v>
@@ -2752,9 +3652,8 @@
       <c r="D56" t="s">
         <v>71</v>
       </c>
-      <c r="E56" s="6" t="str" cm="1">
-        <f t="array" ref="E56">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-09-2026 19:05</v>
+      <c r="E56" s="6" t="s">
+        <v>446</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>8</v>
@@ -2770,9 +3669,8 @@
       <c r="D57" t="s">
         <v>71</v>
       </c>
-      <c r="E57" s="6" t="str" cm="1">
-        <f t="array" ref="E57">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-09-2026 21:05</v>
+      <c r="E57" s="6" t="s">
+        <v>447</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>8</v>
@@ -2788,9 +3686,8 @@
       <c r="D58" t="s">
         <v>71</v>
       </c>
-      <c r="E58" s="6" t="str" cm="1">
-        <f t="array" ref="E58">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-09-2026 03:05</v>
+      <c r="E58" s="6" t="s">
+        <v>448</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>8</v>
@@ -2806,9 +3703,8 @@
       <c r="D59" t="s">
         <v>71</v>
       </c>
-      <c r="E59" s="6" t="str" cm="1">
-        <f t="array" ref="E59">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-09-2026 06:05</v>
+      <c r="E59" s="6" t="s">
+        <v>449</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>8</v>
@@ -2824,9 +3720,8 @@
       <c r="D60" t="s">
         <v>71</v>
       </c>
-      <c r="E60" s="6" t="str" cm="1">
-        <f t="array" ref="E60">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-09-2026 08:35</v>
+      <c r="E60" s="6" t="s">
+        <v>450</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>8</v>
@@ -2842,9 +3737,8 @@
       <c r="D61" t="s">
         <v>71</v>
       </c>
-      <c r="E61" s="6" t="str" cm="1">
-        <f t="array" ref="E61">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-09-2026 11:35</v>
+      <c r="E61" s="6" t="s">
+        <v>451</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>8</v>
@@ -2860,9 +3754,8 @@
       <c r="D62" t="s">
         <v>71</v>
       </c>
-      <c r="E62" s="6" t="str" cm="1">
-        <f t="array" ref="E62">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-09-2026 17:35</v>
+      <c r="E62" s="6" t="s">
+        <v>452</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>8</v>
@@ -2878,9 +3771,8 @@
       <c r="D63" t="s">
         <v>71</v>
       </c>
-      <c r="E63" s="6" t="str" cm="1">
-        <f t="array" ref="E63">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-09-2026 19:05</v>
+      <c r="E63" s="6" t="s">
+        <v>453</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>8</v>
@@ -2896,9 +3788,8 @@
       <c r="D64" t="s">
         <v>71</v>
       </c>
-      <c r="E64" s="6" t="str" cm="1">
-        <f t="array" ref="E64">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-09-2026 21:05</v>
+      <c r="E64" s="6" t="s">
+        <v>454</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>8</v>
@@ -2914,9 +3805,8 @@
       <c r="D65" t="s">
         <v>71</v>
       </c>
-      <c r="E65" s="6" t="str" cm="1">
-        <f t="array" ref="E65">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-09-2026 03:05</v>
+      <c r="E65" s="6" t="s">
+        <v>455</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>8</v>
@@ -2932,9 +3822,8 @@
       <c r="D66" t="s">
         <v>71</v>
       </c>
-      <c r="E66" s="6" t="str" cm="1">
-        <f t="array" ref="E66">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-09-2026 06:05</v>
+      <c r="E66" s="6" t="s">
+        <v>456</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>8</v>
@@ -2950,9 +3839,8 @@
       <c r="D67" t="s">
         <v>71</v>
       </c>
-      <c r="E67" s="6" t="str" cm="1">
-        <f t="array" ref="E67">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-09-2026 08:35</v>
+      <c r="E67" s="6" t="s">
+        <v>457</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>8</v>
@@ -2968,9 +3856,8 @@
       <c r="D68" t="s">
         <v>71</v>
       </c>
-      <c r="E68" s="6" t="str" cm="1">
-        <f t="array" ref="E68">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-09-2026 11:35</v>
+      <c r="E68" s="6" t="s">
+        <v>458</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>8</v>
@@ -2986,9 +3873,8 @@
       <c r="D69" t="s">
         <v>71</v>
       </c>
-      <c r="E69" s="6" t="str" cm="1">
-        <f t="array" ref="E69">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-09-2026 17:35</v>
+      <c r="E69" s="6" t="s">
+        <v>459</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>8</v>
@@ -3004,9 +3890,8 @@
       <c r="D70" t="s">
         <v>71</v>
       </c>
-      <c r="E70" s="6" t="str" cm="1">
-        <f t="array" ref="E70">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-09-2026 19:05</v>
+      <c r="E70" s="6" t="s">
+        <v>460</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>8</v>
@@ -3022,9 +3907,8 @@
       <c r="D71" t="s">
         <v>71</v>
       </c>
-      <c r="E71" s="6" t="str" cm="1">
-        <f t="array" ref="E71">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-09-2026 21:05</v>
+      <c r="E71" s="6" t="s">
+        <v>461</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>8</v>
@@ -3040,9 +3924,8 @@
       <c r="D72" t="s">
         <v>71</v>
       </c>
-      <c r="E72" s="6" t="str" cm="1">
-        <f t="array" ref="E72">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-09-2026 03:05</v>
+      <c r="E72" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>8</v>
@@ -3058,9 +3941,8 @@
       <c r="D73" t="s">
         <v>71</v>
       </c>
-      <c r="E73" s="6" t="str" cm="1">
-        <f t="array" ref="E73">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-09-2026 06:05</v>
+      <c r="E73" s="6" t="s">
+        <v>463</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>8</v>
@@ -3076,9 +3958,8 @@
       <c r="D74" t="s">
         <v>346</v>
       </c>
-      <c r="E74" s="6" t="str" cm="1">
-        <f t="array" ref="E74">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-09-2026 08:35</v>
+      <c r="E74" s="6" t="s">
+        <v>464</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>8</v>
@@ -3094,9 +3975,8 @@
       <c r="D75" t="s">
         <v>346</v>
       </c>
-      <c r="E75" s="6" t="str" cm="1">
-        <f t="array" ref="E75">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-09-2026 11:35</v>
+      <c r="E75" s="6" t="s">
+        <v>465</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>8</v>
@@ -3112,9 +3992,8 @@
       <c r="D76" t="s">
         <v>346</v>
       </c>
-      <c r="E76" s="6" t="str" cm="1">
-        <f t="array" ref="E76">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-09-2026 17:35</v>
+      <c r="E76" s="6">
+        <v>46269.732638888891</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>8</v>
@@ -3130,9 +4009,8 @@
       <c r="D77" t="s">
         <v>346</v>
       </c>
-      <c r="E77" s="6" t="str" cm="1">
-        <f t="array" ref="E77">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-09-2026 19:05</v>
+      <c r="E77" s="6" t="s">
+        <v>466</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>8</v>
@@ -3148,9 +4026,8 @@
       <c r="D78" t="s">
         <v>346</v>
       </c>
-      <c r="E78" s="6" t="str" cm="1">
-        <f t="array" ref="E78">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-09-2026 21:05</v>
+      <c r="E78" s="6" t="s">
+        <v>467</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>8</v>
@@ -3166,9 +4043,8 @@
       <c r="D79" t="s">
         <v>346</v>
       </c>
-      <c r="E79" s="6" t="str" cm="1">
-        <f t="array" ref="E79">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-09-2026 03:05</v>
+      <c r="E79" s="6" t="s">
+        <v>468</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>8</v>
@@ -3184,9 +4060,8 @@
       <c r="D80" t="s">
         <v>346</v>
       </c>
-      <c r="E80" s="6" t="str" cm="1">
-        <f t="array" ref="E80">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-09-2026 06:05</v>
+      <c r="E80" s="6" t="s">
+        <v>469</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>8</v>
@@ -3202,9 +4077,8 @@
       <c r="D81" t="s">
         <v>346</v>
       </c>
-      <c r="E81" s="6" t="str" cm="1">
-        <f t="array" ref="E81">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-09-2026 08:35</v>
+      <c r="E81" s="6" t="s">
+        <v>470</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>8</v>
@@ -3220,9 +4094,8 @@
       <c r="D82" t="s">
         <v>346</v>
       </c>
-      <c r="E82" s="6" t="str" cm="1">
-        <f t="array" ref="E82">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-09-2026 11:35</v>
+      <c r="E82" s="6" t="s">
+        <v>471</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>8</v>
@@ -3238,9 +4111,8 @@
       <c r="D83" t="s">
         <v>346</v>
       </c>
-      <c r="E83" s="6" t="str" cm="1">
-        <f t="array" ref="E83">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-09-2026 17:35</v>
+      <c r="E83" s="6" t="s">
+        <v>472</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>8</v>
@@ -3256,9 +4128,8 @@
       <c r="D84" t="s">
         <v>346</v>
       </c>
-      <c r="E84" s="6" t="str" cm="1">
-        <f t="array" ref="E84">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-09-2026 19:05</v>
+      <c r="E84" s="6" t="s">
+        <v>473</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>8</v>
@@ -3274,9 +4145,8 @@
       <c r="D85" t="s">
         <v>346</v>
       </c>
-      <c r="E85" s="6" t="str" cm="1">
-        <f t="array" ref="E85">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-09-2026 21:05</v>
+      <c r="E85" s="6" t="s">
+        <v>474</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>8</v>
@@ -3292,9 +4162,8 @@
       <c r="D86" t="s">
         <v>346</v>
       </c>
-      <c r="E86" s="6" t="str" cm="1">
-        <f t="array" ref="E86">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-09-2026 03:05</v>
+      <c r="E86" s="6" t="s">
+        <v>475</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>8</v>
@@ -3310,9 +4179,8 @@
       <c r="D87" t="s">
         <v>346</v>
       </c>
-      <c r="E87" s="6" t="str" cm="1">
-        <f t="array" ref="E87">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-09-2026 06:05</v>
+      <c r="E87" s="6" t="s">
+        <v>476</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>8</v>
@@ -3328,9 +4196,8 @@
       <c r="D88" t="s">
         <v>346</v>
       </c>
-      <c r="E88" s="6" t="str" cm="1">
-        <f t="array" ref="E88">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-09-2026 08:35</v>
+      <c r="E88" s="6" t="s">
+        <v>477</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>8</v>
@@ -3346,9 +4213,8 @@
       <c r="D89" t="s">
         <v>346</v>
       </c>
-      <c r="E89" s="6" t="str" cm="1">
-        <f t="array" ref="E89">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-09-2026 11:35</v>
+      <c r="E89" s="6" t="s">
+        <v>478</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>8</v>
@@ -3364,9 +4230,8 @@
       <c r="D90" t="s">
         <v>346</v>
       </c>
-      <c r="E90" s="6" t="str" cm="1">
-        <f t="array" ref="E90">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-09-2026 17:35</v>
+      <c r="E90" s="6" t="s">
+        <v>479</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>8</v>
@@ -3382,9 +4247,8 @@
       <c r="D91" t="s">
         <v>346</v>
       </c>
-      <c r="E91" s="6" t="str" cm="1">
-        <f t="array" ref="E91">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-09-2026 19:05</v>
+      <c r="E91" s="6" t="s">
+        <v>480</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>8</v>
@@ -3400,9 +4264,8 @@
       <c r="D92" t="s">
         <v>346</v>
       </c>
-      <c r="E92" s="6" t="str" cm="1">
-        <f t="array" ref="E92">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-09-2026 21:05</v>
+      <c r="E92" s="6" t="s">
+        <v>481</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>8</v>
@@ -3418,9 +4281,8 @@
       <c r="D93" t="s">
         <v>346</v>
       </c>
-      <c r="E93" s="6" t="str" cm="1">
-        <f t="array" ref="E93">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-09-2026 03:05</v>
+      <c r="E93" s="6" t="s">
+        <v>482</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>8</v>
@@ -3436,9 +4298,8 @@
       <c r="D94" t="s">
         <v>346</v>
       </c>
-      <c r="E94" s="6" t="str" cm="1">
-        <f t="array" ref="E94">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-09-2026 06:05</v>
+      <c r="E94" s="6" t="s">
+        <v>483</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>8</v>
@@ -3454,9 +4315,8 @@
       <c r="D95" t="s">
         <v>346</v>
       </c>
-      <c r="E95" s="6" t="str" cm="1">
-        <f t="array" ref="E95">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-09-2026 08:35</v>
+      <c r="E95" s="6" t="s">
+        <v>484</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>8</v>
@@ -3472,9 +4332,8 @@
       <c r="D96" t="s">
         <v>346</v>
       </c>
-      <c r="E96" s="6" t="str" cm="1">
-        <f t="array" ref="E96">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-09-2026 11:35</v>
+      <c r="E96" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>8</v>
@@ -3490,9 +4349,8 @@
       <c r="D97" t="s">
         <v>346</v>
       </c>
-      <c r="E97" s="6" t="str" cm="1">
-        <f t="array" ref="E97">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-09-2026 17:35</v>
+      <c r="E97" s="6" t="s">
+        <v>486</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>8</v>
@@ -3508,9 +4366,8 @@
       <c r="D98" t="s">
         <v>346</v>
       </c>
-      <c r="E98" s="6" t="str" cm="1">
-        <f t="array" ref="E98">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-09-2026 19:05</v>
+      <c r="E98" s="6" t="s">
+        <v>487</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>8</v>
@@ -3526,9 +4383,8 @@
       <c r="D99" t="s">
         <v>346</v>
       </c>
-      <c r="E99" s="6" t="str" cm="1">
-        <f t="array" ref="E99">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-09-2026 21:05</v>
+      <c r="E99" s="6" t="s">
+        <v>488</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>8</v>
@@ -3544,9 +4400,8 @@
       <c r="D100" t="s">
         <v>346</v>
       </c>
-      <c r="E100" s="6" t="str" cm="1">
-        <f t="array" ref="E100">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-09-2026 03:05</v>
+      <c r="E100" s="6" t="s">
+        <v>489</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>8</v>
@@ -3562,9 +4417,8 @@
       <c r="D101" t="s">
         <v>346</v>
       </c>
-      <c r="E101" s="6" t="str" cm="1">
-        <f t="array" ref="E101">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-09-2026 06:05</v>
+      <c r="E101" s="6" t="s">
+        <v>490</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>8</v>
@@ -3580,9 +4434,8 @@
       <c r="D102" t="s">
         <v>346</v>
       </c>
-      <c r="E102" s="6" t="str" cm="1">
-        <f t="array" ref="E102">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-09-2026 08:35</v>
+      <c r="E102" s="6" t="s">
+        <v>491</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>8</v>
@@ -3598,9 +4451,8 @@
       <c r="D103" t="s">
         <v>346</v>
       </c>
-      <c r="E103" s="6" t="str" cm="1">
-        <f t="array" ref="E103">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-09-2026 11:35</v>
+      <c r="E103" s="6" t="s">
+        <v>492</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>8</v>
@@ -3616,9 +4468,8 @@
       <c r="D104" t="s">
         <v>346</v>
       </c>
-      <c r="E104" s="6" t="str" cm="1">
-        <f t="array" ref="E104">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-09-2026 17:35</v>
+      <c r="E104" s="6" t="s">
+        <v>493</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>8</v>
@@ -3634,9 +4485,8 @@
       <c r="D105" t="s">
         <v>346</v>
       </c>
-      <c r="E105" s="6" t="str" cm="1">
-        <f t="array" ref="E105">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-09-2026 19:05</v>
+      <c r="E105" s="6" t="s">
+        <v>494</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>8</v>
@@ -3652,9 +4502,8 @@
       <c r="D106" t="s">
         <v>346</v>
       </c>
-      <c r="E106" s="6" t="str" cm="1">
-        <f t="array" ref="E106">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-09-2026 21:05</v>
+      <c r="E106" s="6" t="s">
+        <v>495</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>8</v>
@@ -3670,9 +4519,8 @@
       <c r="D107" t="s">
         <v>346</v>
       </c>
-      <c r="E107" s="6" t="str" cm="1">
-        <f t="array" ref="E107">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-09-2026 03:05</v>
+      <c r="E107" s="6" t="s">
+        <v>496</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>8</v>
@@ -3688,9 +4536,8 @@
       <c r="D108" t="s">
         <v>346</v>
       </c>
-      <c r="E108" s="6" t="str" cm="1">
-        <f t="array" ref="E108">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-09-2026 06:05</v>
+      <c r="E108" s="6" t="s">
+        <v>497</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>8</v>
@@ -3706,9 +4553,8 @@
       <c r="D109" t="s">
         <v>346</v>
       </c>
-      <c r="E109" s="6" t="str" cm="1">
-        <f t="array" ref="E109">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-09-2026 08:35</v>
+      <c r="E109" s="6" t="s">
+        <v>498</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>8</v>
@@ -3724,9 +4570,8 @@
       <c r="D110" t="s">
         <v>347</v>
       </c>
-      <c r="E110" s="6" t="str" cm="1">
-        <f t="array" ref="E110">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-09-2026 11:35</v>
+      <c r="E110" s="6" t="s">
+        <v>499</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>8</v>
@@ -3742,9 +4587,8 @@
       <c r="D111" t="s">
         <v>347</v>
       </c>
-      <c r="E111" s="6" t="str" cm="1">
-        <f t="array" ref="E111">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-09-2026 17:35</v>
+      <c r="E111" s="6" t="s">
+        <v>500</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>8</v>
@@ -3760,9 +4604,8 @@
       <c r="D112" t="s">
         <v>347</v>
       </c>
-      <c r="E112" s="6" t="str" cm="1">
-        <f t="array" ref="E112">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-09-2026 19:05</v>
+      <c r="E112" s="6" t="s">
+        <v>501</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>8</v>
@@ -3778,9 +4621,8 @@
       <c r="D113" t="s">
         <v>347</v>
       </c>
-      <c r="E113" s="6" t="str" cm="1">
-        <f t="array" ref="E113">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-09-2026 21:05</v>
+      <c r="E113" s="6" t="s">
+        <v>502</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>8</v>
@@ -3796,9 +4638,8 @@
       <c r="D114" t="s">
         <v>347</v>
       </c>
-      <c r="E114" s="6" t="str" cm="1">
-        <f t="array" ref="E114">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-09-2026 03:05</v>
+      <c r="E114" s="6" t="s">
+        <v>503</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>8</v>
@@ -3814,9 +4655,8 @@
       <c r="D115" t="s">
         <v>347</v>
       </c>
-      <c r="E115" s="6" t="str" cm="1">
-        <f t="array" ref="E115">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-09-2026 06:05</v>
+      <c r="E115" s="6" t="s">
+        <v>504</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>8</v>
@@ -3832,9 +4672,8 @@
       <c r="D116" t="s">
         <v>347</v>
       </c>
-      <c r="E116" s="6" t="str" cm="1">
-        <f t="array" ref="E116">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-09-2026 08:35</v>
+      <c r="E116" s="6" t="s">
+        <v>505</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>8</v>
@@ -3850,9 +4689,8 @@
       <c r="D117" t="s">
         <v>347</v>
       </c>
-      <c r="E117" s="6" t="str" cm="1">
-        <f t="array" ref="E117">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-09-2026 11:35</v>
+      <c r="E117" s="6" t="s">
+        <v>506</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>8</v>
@@ -3868,9 +4706,8 @@
       <c r="D118" t="s">
         <v>347</v>
       </c>
-      <c r="E118" s="6" t="str" cm="1">
-        <f t="array" ref="E118">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-09-2026 17:35</v>
+      <c r="E118" s="6" t="s">
+        <v>507</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>8</v>
@@ -3886,9 +4723,8 @@
       <c r="D119" t="s">
         <v>347</v>
       </c>
-      <c r="E119" s="6" t="str" cm="1">
-        <f t="array" ref="E119">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-09-2026 19:05</v>
+      <c r="E119" s="6" t="s">
+        <v>508</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>8</v>
@@ -3904,9 +4740,8 @@
       <c r="D120" t="s">
         <v>347</v>
       </c>
-      <c r="E120" s="6" t="str" cm="1">
-        <f t="array" ref="E120">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-09-2026 21:05</v>
+      <c r="E120" s="6" t="s">
+        <v>509</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>8</v>
@@ -3922,9 +4757,8 @@
       <c r="D121" t="s">
         <v>347</v>
       </c>
-      <c r="E121" s="6" t="str" cm="1">
-        <f t="array" ref="E121">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>11-09-2026 03:05</v>
+      <c r="E121" s="6" t="s">
+        <v>510</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>8</v>
@@ -3940,9 +4774,8 @@
       <c r="D122" t="s">
         <v>347</v>
       </c>
-      <c r="E122" s="6" t="str" cm="1">
-        <f t="array" ref="E122">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>11-09-2026 06:05</v>
+      <c r="E122" s="6" t="s">
+        <v>511</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>8</v>
@@ -3958,9 +4791,8 @@
       <c r="D123" t="s">
         <v>347</v>
       </c>
-      <c r="E123" s="6" t="str" cm="1">
-        <f t="array" ref="E123">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>11-09-2026 08:35</v>
+      <c r="E123" s="6" t="s">
+        <v>512</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>8</v>
@@ -3976,9 +4808,8 @@
       <c r="D124" t="s">
         <v>347</v>
       </c>
-      <c r="E124" s="6" t="str" cm="1">
-        <f t="array" ref="E124">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>11-09-2026 11:35</v>
+      <c r="E124" s="6" t="s">
+        <v>513</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>8</v>
@@ -3994,9 +4825,8 @@
       <c r="D125" t="s">
         <v>347</v>
       </c>
-      <c r="E125" s="6" t="str" cm="1">
-        <f t="array" ref="E125">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>11-09-2026 17:35</v>
+      <c r="E125" s="6" t="s">
+        <v>514</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>8</v>
@@ -4012,9 +4842,8 @@
       <c r="D126" t="s">
         <v>347</v>
       </c>
-      <c r="E126" s="6" t="str" cm="1">
-        <f t="array" ref="E126">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>11-09-2026 19:05</v>
+      <c r="E126" s="6" t="s">
+        <v>515</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>8</v>
@@ -4030,9 +4859,8 @@
       <c r="D127" t="s">
         <v>347</v>
       </c>
-      <c r="E127" s="6" t="str" cm="1">
-        <f t="array" ref="E127">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>11-09-2026 21:05</v>
+      <c r="E127" s="6" t="s">
+        <v>516</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>8</v>
@@ -4048,9 +4876,8 @@
       <c r="D128" t="s">
         <v>347</v>
       </c>
-      <c r="E128" s="6" t="str" cm="1">
-        <f t="array" ref="E128">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>12-09-2026 03:05</v>
+      <c r="E128" s="6" t="s">
+        <v>517</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>8</v>
@@ -4066,9 +4893,8 @@
       <c r="D129" t="s">
         <v>347</v>
       </c>
-      <c r="E129" s="6" t="str" cm="1">
-        <f t="array" ref="E129">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>12-09-2026 06:05</v>
+      <c r="E129" s="6" t="s">
+        <v>518</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>8</v>
@@ -4084,9 +4910,8 @@
       <c r="D130" t="s">
         <v>347</v>
       </c>
-      <c r="E130" s="6" t="str" cm="1">
-        <f t="array" ref="E130">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>12-09-2026 08:35</v>
+      <c r="E130" s="6" t="s">
+        <v>519</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>8</v>
@@ -4102,9 +4927,8 @@
       <c r="D131" t="s">
         <v>347</v>
       </c>
-      <c r="E131" s="6" t="str" cm="1">
-        <f t="array" ref="E131">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>12-09-2026 11:35</v>
+      <c r="E131" s="6" t="s">
+        <v>520</v>
       </c>
       <c r="F131" s="4" t="s">
         <v>8</v>
@@ -4120,9 +4944,8 @@
       <c r="D132" t="s">
         <v>347</v>
       </c>
-      <c r="E132" s="6" t="str" cm="1">
-        <f t="array" ref="E132">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>12-09-2026 17:35</v>
+      <c r="E132" s="6" t="s">
+        <v>521</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>8</v>
@@ -4138,9 +4961,8 @@
       <c r="D133" t="s">
         <v>347</v>
       </c>
-      <c r="E133" s="6" t="str" cm="1">
-        <f t="array" ref="E133">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>12-09-2026 19:05</v>
+      <c r="E133" s="6" t="s">
+        <v>522</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>8</v>
@@ -4156,9 +4978,8 @@
       <c r="D134" t="s">
         <v>347</v>
       </c>
-      <c r="E134" s="6" t="str" cm="1">
-        <f t="array" ref="E134">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>12-09-2026 21:05</v>
+      <c r="E134" s="6" t="s">
+        <v>523</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>8</v>
@@ -4174,9 +4995,8 @@
       <c r="D135" t="s">
         <v>347</v>
       </c>
-      <c r="E135" s="6" t="str" cm="1">
-        <f t="array" ref="E135">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>13-09-2026 03:05</v>
+      <c r="E135" s="6" t="s">
+        <v>524</v>
       </c>
       <c r="F135" s="4" t="s">
         <v>8</v>
@@ -4192,9 +5012,8 @@
       <c r="D136" t="s">
         <v>347</v>
       </c>
-      <c r="E136" s="6" t="str" cm="1">
-        <f t="array" ref="E136">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>13-09-2026 06:05</v>
+      <c r="E136" s="6" t="s">
+        <v>525</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>8</v>
@@ -4210,9 +5029,8 @@
       <c r="D137" t="s">
         <v>347</v>
       </c>
-      <c r="E137" s="6" t="str" cm="1">
-        <f t="array" ref="E137">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>13-09-2026 08:35</v>
+      <c r="E137" s="6" t="s">
+        <v>526</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>8</v>
@@ -4228,9 +5046,8 @@
       <c r="D138" t="s">
         <v>347</v>
       </c>
-      <c r="E138" s="6" t="str" cm="1">
-        <f t="array" ref="E138">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>13-09-2026 11:35</v>
+      <c r="E138" s="6" t="s">
+        <v>527</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>8</v>
@@ -4246,9 +5063,8 @@
       <c r="D139" t="s">
         <v>347</v>
       </c>
-      <c r="E139" s="6" t="str" cm="1">
-        <f t="array" ref="E139">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>13-09-2026 17:35</v>
+      <c r="E139" s="6" t="s">
+        <v>528</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>8</v>
@@ -4264,9 +5080,8 @@
       <c r="D140" t="s">
         <v>347</v>
       </c>
-      <c r="E140" s="6" t="str" cm="1">
-        <f t="array" ref="E140">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>13-09-2026 19:05</v>
+      <c r="E140" s="6" t="s">
+        <v>529</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>8</v>
@@ -4282,9 +5097,8 @@
       <c r="D141" t="s">
         <v>347</v>
       </c>
-      <c r="E141" s="6" t="str" cm="1">
-        <f t="array" ref="E141">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>13-09-2026 21:05</v>
+      <c r="E141" s="6" t="s">
+        <v>530</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>8</v>
@@ -4300,9 +5114,8 @@
       <c r="D142" t="s">
         <v>347</v>
       </c>
-      <c r="E142" s="6" t="str" cm="1">
-        <f t="array" ref="E142">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>14-09-2026 03:05</v>
+      <c r="E142" s="6" t="s">
+        <v>531</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>8</v>
@@ -4318,9 +5131,8 @@
       <c r="D143" t="s">
         <v>348</v>
       </c>
-      <c r="E143" s="6" t="str" cm="1">
-        <f t="array" ref="E143">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>14-09-2026 06:05</v>
+      <c r="E143" s="6" t="s">
+        <v>532</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>8</v>
@@ -4336,9 +5148,8 @@
       <c r="D144" t="s">
         <v>348</v>
       </c>
-      <c r="E144" s="6" t="str" cm="1">
-        <f t="array" ref="E144">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>14-09-2026 08:35</v>
+      <c r="E144" s="6" t="s">
+        <v>533</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>8</v>
@@ -4354,9 +5165,8 @@
       <c r="D145" t="s">
         <v>348</v>
       </c>
-      <c r="E145" s="6" t="str" cm="1">
-        <f t="array" ref="E145">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>14-09-2026 11:35</v>
+      <c r="E145" s="6" t="s">
+        <v>534</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>8</v>
@@ -4372,9 +5182,8 @@
       <c r="D146" t="s">
         <v>348</v>
       </c>
-      <c r="E146" s="6" t="str" cm="1">
-        <f t="array" ref="E146">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>14-09-2026 17:35</v>
+      <c r="E146" s="6" t="s">
+        <v>535</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>8</v>
@@ -4390,9 +5199,8 @@
       <c r="D147" t="s">
         <v>348</v>
       </c>
-      <c r="E147" s="6" t="str" cm="1">
-        <f t="array" ref="E147">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>14-09-2026 19:05</v>
+      <c r="E147" s="6" t="s">
+        <v>536</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>8</v>
@@ -4408,9 +5216,8 @@
       <c r="D148" t="s">
         <v>348</v>
       </c>
-      <c r="E148" s="6" t="str" cm="1">
-        <f t="array" ref="E148">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>14-09-2026 21:05</v>
+      <c r="E148" s="6" t="s">
+        <v>537</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>8</v>
@@ -4426,9 +5233,8 @@
       <c r="D149" t="s">
         <v>348</v>
       </c>
-      <c r="E149" s="6" t="str" cm="1">
-        <f t="array" ref="E149">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>15-09-2026 03:05</v>
+      <c r="E149" s="6" t="s">
+        <v>538</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>8</v>
@@ -4444,9 +5250,8 @@
       <c r="D150" t="s">
         <v>348</v>
       </c>
-      <c r="E150" s="6" t="str" cm="1">
-        <f t="array" ref="E150">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>15-09-2026 06:05</v>
+      <c r="E150" s="6" t="s">
+        <v>539</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>8</v>
@@ -4462,9 +5267,8 @@
       <c r="D151" t="s">
         <v>348</v>
       </c>
-      <c r="E151" s="6" t="str" cm="1">
-        <f t="array" ref="E151">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>15-09-2026 08:35</v>
+      <c r="E151" s="6" t="s">
+        <v>540</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>8</v>
@@ -4480,9 +5284,8 @@
       <c r="D152" t="s">
         <v>348</v>
       </c>
-      <c r="E152" s="6" t="str" cm="1">
-        <f t="array" ref="E152">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>15-09-2026 11:35</v>
+      <c r="E152" s="6" t="s">
+        <v>541</v>
       </c>
       <c r="F152" s="4" t="s">
         <v>8</v>
@@ -4498,9 +5301,8 @@
       <c r="D153" t="s">
         <v>348</v>
       </c>
-      <c r="E153" s="6" t="str" cm="1">
-        <f t="array" ref="E153">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>15-09-2026 17:35</v>
+      <c r="E153" s="6" t="s">
+        <v>542</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>8</v>
@@ -4516,9 +5318,8 @@
       <c r="D154" t="s">
         <v>348</v>
       </c>
-      <c r="E154" s="6" t="str" cm="1">
-        <f t="array" ref="E154">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>15-09-2026 19:05</v>
+      <c r="E154" s="6" t="s">
+        <v>543</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>8</v>
@@ -4534,9 +5335,8 @@
       <c r="D155" t="s">
         <v>348</v>
       </c>
-      <c r="E155" s="6" t="str" cm="1">
-        <f t="array" ref="E155">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>15-09-2026 21:05</v>
+      <c r="E155" s="6" t="s">
+        <v>544</v>
       </c>
       <c r="F155" s="4" t="s">
         <v>8</v>
@@ -4552,9 +5352,8 @@
       <c r="D156" t="s">
         <v>348</v>
       </c>
-      <c r="E156" s="6" t="str" cm="1">
-        <f t="array" ref="E156">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>16-09-2026 03:05</v>
+      <c r="E156" s="6" t="s">
+        <v>545</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>8</v>
@@ -4570,9 +5369,8 @@
       <c r="D157" t="s">
         <v>348</v>
       </c>
-      <c r="E157" s="6" t="str" cm="1">
-        <f t="array" ref="E157">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>16-09-2026 06:05</v>
+      <c r="E157" s="6" t="s">
+        <v>546</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>8</v>
@@ -4588,9 +5386,8 @@
       <c r="D158" t="s">
         <v>348</v>
       </c>
-      <c r="E158" s="6" t="str" cm="1">
-        <f t="array" ref="E158">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>16-09-2026 08:35</v>
+      <c r="E158" s="6" t="s">
+        <v>547</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>8</v>
@@ -4606,9 +5403,8 @@
       <c r="D159" t="s">
         <v>348</v>
       </c>
-      <c r="E159" s="6" t="str" cm="1">
-        <f t="array" ref="E159">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>16-09-2026 11:35</v>
+      <c r="E159" s="6" t="s">
+        <v>548</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>8</v>
@@ -4624,9 +5420,8 @@
       <c r="D160" t="s">
         <v>348</v>
       </c>
-      <c r="E160" s="6" t="str" cm="1">
-        <f t="array" ref="E160">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>16-09-2026 17:35</v>
+      <c r="E160" s="6" t="s">
+        <v>549</v>
       </c>
       <c r="F160" s="4" t="s">
         <v>8</v>
@@ -4642,9 +5437,8 @@
       <c r="D161" t="s">
         <v>348</v>
       </c>
-      <c r="E161" s="6" t="str" cm="1">
-        <f t="array" ref="E161">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>16-09-2026 19:05</v>
+      <c r="E161" s="6" t="s">
+        <v>550</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>8</v>
@@ -4660,9 +5454,8 @@
       <c r="D162" t="s">
         <v>348</v>
       </c>
-      <c r="E162" s="6" t="str" cm="1">
-        <f t="array" ref="E162">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>16-09-2026 21:05</v>
+      <c r="E162" s="6" t="s">
+        <v>551</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>8</v>
@@ -4678,9 +5471,8 @@
       <c r="D163" t="s">
         <v>348</v>
       </c>
-      <c r="E163" s="6" t="str" cm="1">
-        <f t="array" ref="E163">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>17-09-2026 03:05</v>
+      <c r="E163" s="6" t="s">
+        <v>552</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>8</v>
@@ -4696,9 +5488,8 @@
       <c r="D164" t="s">
         <v>348</v>
       </c>
-      <c r="E164" s="6" t="str" cm="1">
-        <f t="array" ref="E164">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>17-09-2026 06:05</v>
+      <c r="E164" s="6" t="s">
+        <v>553</v>
       </c>
       <c r="F164" s="4" t="s">
         <v>8</v>
@@ -4714,9 +5505,8 @@
       <c r="D165" t="s">
         <v>348</v>
       </c>
-      <c r="E165" s="6" t="str" cm="1">
-        <f t="array" ref="E165">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>17-09-2026 08:35</v>
+      <c r="E165" s="6" t="s">
+        <v>554</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>8</v>
@@ -4732,9 +5522,8 @@
       <c r="D166" t="s">
         <v>348</v>
       </c>
-      <c r="E166" s="6" t="str" cm="1">
-        <f t="array" ref="E166">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>17-09-2026 11:35</v>
+      <c r="E166" s="6" t="s">
+        <v>555</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>8</v>
@@ -4750,9 +5539,8 @@
       <c r="D167" t="s">
         <v>348</v>
       </c>
-      <c r="E167" s="6" t="str" cm="1">
-        <f t="array" ref="E167">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>17-09-2026 17:35</v>
+      <c r="E167" s="6" t="s">
+        <v>556</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>8</v>
@@ -4768,9 +5556,8 @@
       <c r="D168" t="s">
         <v>348</v>
       </c>
-      <c r="E168" s="6" t="str" cm="1">
-        <f t="array" ref="E168">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>17-09-2026 19:05</v>
+      <c r="E168" s="6" t="s">
+        <v>557</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>8</v>
@@ -4786,9 +5573,8 @@
       <c r="D169" t="s">
         <v>348</v>
       </c>
-      <c r="E169" s="6" t="str" cm="1">
-        <f t="array" ref="E169">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>17-09-2026 21:05</v>
+      <c r="E169" s="6" t="s">
+        <v>558</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>8</v>
@@ -4804,9 +5590,8 @@
       <c r="D170" t="s">
         <v>348</v>
       </c>
-      <c r="E170" s="6" t="str" cm="1">
-        <f t="array" ref="E170">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>18-09-2026 03:05</v>
+      <c r="E170" s="6" t="s">
+        <v>559</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>8</v>
@@ -4822,9 +5607,8 @@
       <c r="D171" t="s">
         <v>348</v>
       </c>
-      <c r="E171" s="6" t="str" cm="1">
-        <f t="array" ref="E171">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>18-09-2026 06:05</v>
+      <c r="E171" s="6" t="s">
+        <v>560</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>8</v>
@@ -4840,9 +5624,8 @@
       <c r="D172" t="s">
         <v>348</v>
       </c>
-      <c r="E172" s="6" t="str" cm="1">
-        <f t="array" ref="E172">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>18-09-2026 08:35</v>
+      <c r="E172" s="6" t="s">
+        <v>561</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>8</v>
@@ -4858,9 +5641,8 @@
       <c r="D173" t="s">
         <v>348</v>
       </c>
-      <c r="E173" s="6" t="str" cm="1">
-        <f t="array" ref="E173">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>18-09-2026 11:35</v>
+      <c r="E173" s="6" t="s">
+        <v>562</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>8</v>
@@ -4876,9 +5658,8 @@
       <c r="D174" t="s">
         <v>348</v>
       </c>
-      <c r="E174" s="6" t="str" cm="1">
-        <f t="array" ref="E174">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>18-09-2026 17:35</v>
+      <c r="E174" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="F174" s="4" t="s">
         <v>8</v>
@@ -4894,9 +5675,8 @@
       <c r="D175" t="s">
         <v>348</v>
       </c>
-      <c r="E175" s="6" t="str" cm="1">
-        <f t="array" ref="E175">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>18-09-2026 19:05</v>
+      <c r="E175" s="6" t="s">
+        <v>564</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>8</v>
@@ -4912,9 +5692,8 @@
       <c r="D176" t="s">
         <v>348</v>
       </c>
-      <c r="E176" s="6" t="str" cm="1">
-        <f t="array" ref="E176">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>18-09-2026 21:05</v>
+      <c r="E176" s="6" t="s">
+        <v>565</v>
       </c>
       <c r="F176" s="4" t="s">
         <v>8</v>
@@ -4930,9 +5709,8 @@
       <c r="D177" t="s">
         <v>348</v>
       </c>
-      <c r="E177" s="6" t="str" cm="1">
-        <f t="array" ref="E177">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>19-09-2026 03:05</v>
+      <c r="E177" s="6" t="s">
+        <v>566</v>
       </c>
       <c r="F177" s="4" t="s">
         <v>8</v>
@@ -4948,9 +5726,8 @@
       <c r="D178" t="s">
         <v>348</v>
       </c>
-      <c r="E178" s="6" t="str" cm="1">
-        <f t="array" ref="E178">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>19-09-2026 06:05</v>
+      <c r="E178" s="6" t="s">
+        <v>567</v>
       </c>
       <c r="F178" s="4" t="s">
         <v>8</v>
@@ -4966,9 +5743,8 @@
       <c r="D179" t="s">
         <v>348</v>
       </c>
-      <c r="E179" s="6" t="str" cm="1">
-        <f t="array" ref="E179">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>19-09-2026 08:35</v>
+      <c r="E179" s="6" t="s">
+        <v>568</v>
       </c>
       <c r="F179" s="4" t="s">
         <v>8</v>
@@ -4984,9 +5760,8 @@
       <c r="D180" t="s">
         <v>348</v>
       </c>
-      <c r="E180" s="6" t="str" cm="1">
-        <f t="array" ref="E180">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>19-09-2026 11:35</v>
+      <c r="E180" s="6" t="s">
+        <v>569</v>
       </c>
       <c r="F180" s="4" t="s">
         <v>8</v>
@@ -5002,9 +5777,8 @@
       <c r="D181" t="s">
         <v>348</v>
       </c>
-      <c r="E181" s="6" t="str" cm="1">
-        <f t="array" ref="E181">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>19-09-2026 17:35</v>
+      <c r="E181" s="6" t="s">
+        <v>570</v>
       </c>
       <c r="F181" s="4" t="s">
         <v>8</v>
@@ -5020,9 +5794,8 @@
       <c r="D182" t="s">
         <v>348</v>
       </c>
-      <c r="E182" s="6" t="str" cm="1">
-        <f t="array" ref="E182">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>19-09-2026 19:05</v>
+      <c r="E182" s="6" t="s">
+        <v>571</v>
       </c>
       <c r="F182" s="4" t="s">
         <v>8</v>
@@ -5038,9 +5811,8 @@
       <c r="D183" t="s">
         <v>348</v>
       </c>
-      <c r="E183" s="6" t="str" cm="1">
-        <f t="array" ref="E183">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>19-09-2026 21:05</v>
+      <c r="E183" s="6" t="s">
+        <v>572</v>
       </c>
       <c r="F183" s="4" t="s">
         <v>8</v>
@@ -5056,9 +5828,8 @@
       <c r="D184" t="s">
         <v>348</v>
       </c>
-      <c r="E184" s="6" t="str" cm="1">
-        <f t="array" ref="E184">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>20-09-2026 03:05</v>
+      <c r="E184" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="F184" s="4" t="s">
         <v>8</v>
@@ -5074,9 +5845,8 @@
       <c r="D185" t="s">
         <v>348</v>
       </c>
-      <c r="E185" s="6" t="str" cm="1">
-        <f t="array" ref="E185">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>20-09-2026 06:05</v>
+      <c r="E185" s="6" t="s">
+        <v>574</v>
       </c>
       <c r="F185" s="4" t="s">
         <v>8</v>
@@ -5092,9 +5862,8 @@
       <c r="D186" t="s">
         <v>348</v>
       </c>
-      <c r="E186" s="6" t="str" cm="1">
-        <f t="array" ref="E186">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>20-09-2026 08:35</v>
+      <c r="E186" s="6" t="s">
+        <v>575</v>
       </c>
       <c r="F186" s="4" t="s">
         <v>8</v>
@@ -5110,9 +5879,8 @@
       <c r="D187" t="s">
         <v>348</v>
       </c>
-      <c r="E187" s="6" t="str" cm="1">
-        <f t="array" ref="E187">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>20-09-2026 11:35</v>
+      <c r="E187" s="6" t="s">
+        <v>576</v>
       </c>
       <c r="F187" s="4" t="s">
         <v>8</v>
@@ -5128,9 +5896,8 @@
       <c r="D188" t="s">
         <v>348</v>
       </c>
-      <c r="E188" s="6" t="str" cm="1">
-        <f t="array" ref="E188">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>20-09-2026 17:35</v>
+      <c r="E188" s="6" t="s">
+        <v>577</v>
       </c>
       <c r="F188" s="4" t="s">
         <v>8</v>
@@ -5146,9 +5913,8 @@
       <c r="D189" t="s">
         <v>348</v>
       </c>
-      <c r="E189" s="6" t="str" cm="1">
-        <f t="array" ref="E189">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>20-09-2026 19:05</v>
+      <c r="E189" s="6" t="s">
+        <v>578</v>
       </c>
       <c r="F189" s="4" t="s">
         <v>8</v>
@@ -5164,9 +5930,8 @@
       <c r="D190" t="s">
         <v>349</v>
       </c>
-      <c r="E190" s="6" t="str" cm="1">
-        <f t="array" ref="E190">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>20-09-2026 21:05</v>
+      <c r="E190" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="F190" s="4" t="s">
         <v>8</v>
@@ -5182,9 +5947,8 @@
       <c r="D191" t="s">
         <v>349</v>
       </c>
-      <c r="E191" s="6" t="str" cm="1">
-        <f t="array" ref="E191">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>21-09-2026 03:05</v>
+      <c r="E191" s="6" t="s">
+        <v>580</v>
       </c>
       <c r="F191" s="4" t="s">
         <v>8</v>
@@ -5200,9 +5964,8 @@
       <c r="D192" t="s">
         <v>349</v>
       </c>
-      <c r="E192" s="6" t="str" cm="1">
-        <f t="array" ref="E192">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>21-09-2026 06:05</v>
+      <c r="E192" s="6" t="s">
+        <v>581</v>
       </c>
       <c r="F192" s="4" t="s">
         <v>8</v>
@@ -5218,9 +5981,8 @@
       <c r="D193" t="s">
         <v>349</v>
       </c>
-      <c r="E193" s="6" t="str" cm="1">
-        <f t="array" ref="E193">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>21-09-2026 08:35</v>
+      <c r="E193" s="6" t="s">
+        <v>582</v>
       </c>
       <c r="F193" s="4" t="s">
         <v>8</v>
@@ -5236,9 +5998,8 @@
       <c r="D194" t="s">
         <v>349</v>
       </c>
-      <c r="E194" s="6" t="str" cm="1">
-        <f t="array" ref="E194">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>21-09-2026 11:35</v>
+      <c r="E194" s="6" t="s">
+        <v>583</v>
       </c>
       <c r="F194" s="4" t="s">
         <v>8</v>
@@ -5254,9 +6015,8 @@
       <c r="D195" t="s">
         <v>349</v>
       </c>
-      <c r="E195" s="6" t="str" cm="1">
-        <f t="array" ref="E195">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>21-09-2026 17:35</v>
+      <c r="E195" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="F195" s="4" t="s">
         <v>8</v>
@@ -5272,9 +6032,8 @@
       <c r="D196" t="s">
         <v>349</v>
       </c>
-      <c r="E196" s="6" t="str" cm="1">
-        <f t="array" ref="E196">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>21-09-2026 19:05</v>
+      <c r="E196" s="6" t="s">
+        <v>585</v>
       </c>
       <c r="F196" s="4" t="s">
         <v>8</v>
@@ -5290,9 +6049,8 @@
       <c r="D197" t="s">
         <v>349</v>
       </c>
-      <c r="E197" s="6" t="str" cm="1">
-        <f t="array" ref="E197">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>21-09-2026 21:05</v>
+      <c r="E197" s="6" t="s">
+        <v>586</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>8</v>
@@ -5308,9 +6066,8 @@
       <c r="D198" t="s">
         <v>349</v>
       </c>
-      <c r="E198" s="6" t="str" cm="1">
-        <f t="array" ref="E198">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>22-09-2026 03:05</v>
+      <c r="E198" s="6" t="s">
+        <v>587</v>
       </c>
       <c r="F198" s="4" t="s">
         <v>8</v>
@@ -5326,9 +6083,8 @@
       <c r="D199" t="s">
         <v>349</v>
       </c>
-      <c r="E199" s="6" t="str" cm="1">
-        <f t="array" ref="E199">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>22-09-2026 06:05</v>
+      <c r="E199" s="6" t="s">
+        <v>588</v>
       </c>
       <c r="F199" s="4" t="s">
         <v>8</v>
@@ -5344,9 +6100,8 @@
       <c r="D200" t="s">
         <v>349</v>
       </c>
-      <c r="E200" s="6" t="str" cm="1">
-        <f t="array" ref="E200">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>22-09-2026 08:35</v>
+      <c r="E200" s="6" t="s">
+        <v>589</v>
       </c>
       <c r="F200" s="4" t="s">
         <v>8</v>
@@ -5362,9 +6117,8 @@
       <c r="D201" t="s">
         <v>349</v>
       </c>
-      <c r="E201" s="6" t="str" cm="1">
-        <f t="array" ref="E201">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>22-09-2026 11:35</v>
+      <c r="E201" s="6" t="s">
+        <v>590</v>
       </c>
       <c r="F201" s="4" t="s">
         <v>8</v>
@@ -5380,9 +6134,8 @@
       <c r="D202" t="s">
         <v>349</v>
       </c>
-      <c r="E202" s="6" t="str" cm="1">
-        <f t="array" ref="E202">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>22-09-2026 17:35</v>
+      <c r="E202" s="6" t="s">
+        <v>591</v>
       </c>
       <c r="F202" s="4" t="s">
         <v>8</v>
@@ -5398,9 +6151,8 @@
       <c r="D203" t="s">
         <v>349</v>
       </c>
-      <c r="E203" s="6" t="str" cm="1">
-        <f t="array" ref="E203">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>22-09-2026 19:05</v>
+      <c r="E203" s="6" t="s">
+        <v>592</v>
       </c>
       <c r="F203" s="4" t="s">
         <v>8</v>
@@ -5416,9 +6168,8 @@
       <c r="D204" t="s">
         <v>349</v>
       </c>
-      <c r="E204" s="6" t="str" cm="1">
-        <f t="array" ref="E204">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>22-09-2026 21:05</v>
+      <c r="E204" s="6" t="s">
+        <v>593</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>8</v>
@@ -5434,9 +6185,8 @@
       <c r="D205" t="s">
         <v>349</v>
       </c>
-      <c r="E205" s="6" t="str" cm="1">
-        <f t="array" ref="E205">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>23-09-2026 03:05</v>
+      <c r="E205" s="6" t="s">
+        <v>594</v>
       </c>
       <c r="F205" s="4" t="s">
         <v>8</v>
@@ -5452,9 +6202,8 @@
       <c r="D206" t="s">
         <v>349</v>
       </c>
-      <c r="E206" s="6" t="str" cm="1">
-        <f t="array" ref="E206">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>23-09-2026 06:05</v>
+      <c r="E206" s="6" t="s">
+        <v>595</v>
       </c>
       <c r="F206" s="4" t="s">
         <v>8</v>
@@ -5470,9 +6219,8 @@
       <c r="D207" t="s">
         <v>349</v>
       </c>
-      <c r="E207" s="6" t="str" cm="1">
-        <f t="array" ref="E207">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>23-09-2026 08:35</v>
+      <c r="E207" s="6" t="s">
+        <v>596</v>
       </c>
       <c r="F207" s="4" t="s">
         <v>8</v>
@@ -5488,9 +6236,8 @@
       <c r="D208" t="s">
         <v>349</v>
       </c>
-      <c r="E208" s="6" t="str" cm="1">
-        <f t="array" ref="E208">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>23-09-2026 11:35</v>
+      <c r="E208" s="6" t="s">
+        <v>597</v>
       </c>
       <c r="F208" s="4" t="s">
         <v>8</v>
@@ -5506,9 +6253,8 @@
       <c r="D209" t="s">
         <v>349</v>
       </c>
-      <c r="E209" s="6" t="str" cm="1">
-        <f t="array" ref="E209">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>23-09-2026 17:35</v>
+      <c r="E209" s="6" t="s">
+        <v>598</v>
       </c>
       <c r="F209" s="4" t="s">
         <v>8</v>
@@ -5524,9 +6270,8 @@
       <c r="D210" t="s">
         <v>349</v>
       </c>
-      <c r="E210" s="6" t="str" cm="1">
-        <f t="array" ref="E210">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>23-09-2026 19:05</v>
+      <c r="E210" s="6" t="s">
+        <v>599</v>
       </c>
       <c r="F210" s="4" t="s">
         <v>8</v>
@@ -5542,9 +6287,8 @@
       <c r="D211" t="s">
         <v>349</v>
       </c>
-      <c r="E211" s="6" t="str" cm="1">
-        <f t="array" ref="E211">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>23-09-2026 21:05</v>
+      <c r="E211" s="6" t="s">
+        <v>600</v>
       </c>
       <c r="F211" s="4" t="s">
         <v>8</v>
@@ -5560,9 +6304,8 @@
       <c r="D212" t="s">
         <v>349</v>
       </c>
-      <c r="E212" s="6" t="str" cm="1">
-        <f t="array" ref="E212">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>24-09-2026 03:05</v>
+      <c r="E212" s="6" t="s">
+        <v>601</v>
       </c>
       <c r="F212" s="4" t="s">
         <v>8</v>
@@ -5578,9 +6321,8 @@
       <c r="D213" t="s">
         <v>349</v>
       </c>
-      <c r="E213" s="6" t="str" cm="1">
-        <f t="array" ref="E213">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>24-09-2026 06:05</v>
+      <c r="E213" s="6" t="s">
+        <v>602</v>
       </c>
       <c r="F213" s="4" t="s">
         <v>8</v>
@@ -5596,9 +6338,8 @@
       <c r="D214" t="s">
         <v>349</v>
       </c>
-      <c r="E214" s="6" t="str" cm="1">
-        <f t="array" ref="E214">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>24-09-2026 08:35</v>
+      <c r="E214" s="6" t="s">
+        <v>603</v>
       </c>
       <c r="F214" s="4" t="s">
         <v>8</v>
@@ -5614,9 +6355,8 @@
       <c r="D215" t="s">
         <v>349</v>
       </c>
-      <c r="E215" s="6" t="str" cm="1">
-        <f t="array" ref="E215">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>24-09-2026 11:35</v>
+      <c r="E215" s="6" t="s">
+        <v>604</v>
       </c>
       <c r="F215" s="4" t="s">
         <v>8</v>
@@ -5632,9 +6372,8 @@
       <c r="D216" t="s">
         <v>349</v>
       </c>
-      <c r="E216" s="6" t="str" cm="1">
-        <f t="array" ref="E216">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>24-09-2026 17:35</v>
+      <c r="E216" s="6" t="s">
+        <v>605</v>
       </c>
       <c r="F216" s="4" t="s">
         <v>8</v>
@@ -5650,9 +6389,8 @@
       <c r="D217" t="s">
         <v>349</v>
       </c>
-      <c r="E217" s="6" t="str" cm="1">
-        <f t="array" ref="E217">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>24-09-2026 19:05</v>
+      <c r="E217" s="6" t="s">
+        <v>606</v>
       </c>
       <c r="F217" s="4" t="s">
         <v>8</v>
@@ -5668,9 +6406,8 @@
       <c r="D218" t="s">
         <v>349</v>
       </c>
-      <c r="E218" s="6" t="str" cm="1">
-        <f t="array" ref="E218">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>24-09-2026 21:05</v>
+      <c r="E218" s="6" t="s">
+        <v>607</v>
       </c>
       <c r="F218" s="4" t="s">
         <v>8</v>
@@ -5686,9 +6423,8 @@
       <c r="D219" t="s">
         <v>349</v>
       </c>
-      <c r="E219" s="6" t="str" cm="1">
-        <f t="array" ref="E219">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>25-09-2026 03:05</v>
+      <c r="E219" s="6" t="s">
+        <v>608</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>8</v>
@@ -5704,9 +6440,8 @@
       <c r="D220" t="s">
         <v>349</v>
       </c>
-      <c r="E220" s="6" t="str" cm="1">
-        <f t="array" ref="E220">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>25-09-2026 06:05</v>
+      <c r="E220" s="6" t="s">
+        <v>609</v>
       </c>
       <c r="F220" s="4" t="s">
         <v>8</v>
@@ -5722,9 +6457,8 @@
       <c r="D221" t="s">
         <v>349</v>
       </c>
-      <c r="E221" s="6" t="str" cm="1">
-        <f t="array" ref="E221">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>25-09-2026 08:35</v>
+      <c r="E221" s="6" t="s">
+        <v>610</v>
       </c>
       <c r="F221" s="4" t="s">
         <v>8</v>
@@ -5740,9 +6474,8 @@
       <c r="D222" t="s">
         <v>349</v>
       </c>
-      <c r="E222" s="6" t="str" cm="1">
-        <f t="array" ref="E222">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>25-09-2026 11:35</v>
+      <c r="E222" s="6" t="s">
+        <v>611</v>
       </c>
       <c r="F222" s="4" t="s">
         <v>8</v>
@@ -5758,9 +6491,8 @@
       <c r="D223" t="s">
         <v>349</v>
       </c>
-      <c r="E223" s="6" t="str" cm="1">
-        <f t="array" ref="E223">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>25-09-2026 17:35</v>
+      <c r="E223" s="6" t="s">
+        <v>612</v>
       </c>
       <c r="F223" s="4" t="s">
         <v>8</v>
@@ -5776,9 +6508,8 @@
       <c r="D224" t="s">
         <v>349</v>
       </c>
-      <c r="E224" s="6" t="str" cm="1">
-        <f t="array" ref="E224">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>25-09-2026 19:05</v>
+      <c r="E224" s="6" t="s">
+        <v>613</v>
       </c>
       <c r="F224" s="4" t="s">
         <v>8</v>
@@ -5794,9 +6525,8 @@
       <c r="D225" t="s">
         <v>349</v>
       </c>
-      <c r="E225" s="6" t="str" cm="1">
-        <f t="array" ref="E225">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>25-09-2026 21:05</v>
+      <c r="E225" s="6" t="s">
+        <v>614</v>
       </c>
       <c r="F225" s="4" t="s">
         <v>8</v>
@@ -5812,9 +6542,8 @@
       <c r="D226" t="s">
         <v>349</v>
       </c>
-      <c r="E226" s="6" t="str" cm="1">
-        <f t="array" ref="E226">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-09-2026 03:05</v>
+      <c r="E226" s="6" t="s">
+        <v>615</v>
       </c>
       <c r="F226" s="4" t="s">
         <v>8</v>
@@ -5830,9 +6559,8 @@
       <c r="D227" t="s">
         <v>349</v>
       </c>
-      <c r="E227" s="6" t="str" cm="1">
-        <f t="array" ref="E227">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-09-2026 06:05</v>
+      <c r="E227" s="6" t="s">
+        <v>616</v>
       </c>
       <c r="F227" s="4" t="s">
         <v>8</v>
@@ -5848,9 +6576,8 @@
       <c r="D228" t="s">
         <v>349</v>
       </c>
-      <c r="E228" s="6" t="str" cm="1">
-        <f t="array" ref="E228">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-09-2026 08:35</v>
+      <c r="E228" s="6" t="s">
+        <v>617</v>
       </c>
       <c r="F228" s="4" t="s">
         <v>8</v>
@@ -5866,9 +6593,8 @@
       <c r="D229" t="s">
         <v>349</v>
       </c>
-      <c r="E229" s="6" t="str" cm="1">
-        <f t="array" ref="E229">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-09-2026 11:35</v>
+      <c r="E229" s="6" t="s">
+        <v>618</v>
       </c>
       <c r="F229" s="4" t="s">
         <v>8</v>
@@ -5884,9 +6610,8 @@
       <c r="D230" t="s">
         <v>350</v>
       </c>
-      <c r="E230" s="6" t="str" cm="1">
-        <f t="array" ref="E230">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-09-2026 17:35</v>
+      <c r="E230" s="6" t="s">
+        <v>619</v>
       </c>
       <c r="F230" s="4" t="s">
         <v>8</v>
@@ -5902,9 +6627,8 @@
       <c r="D231" t="s">
         <v>350</v>
       </c>
-      <c r="E231" s="6" t="str" cm="1">
-        <f t="array" ref="E231">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-09-2026 19:05</v>
+      <c r="E231" s="6" t="s">
+        <v>620</v>
       </c>
       <c r="F231" s="4" t="s">
         <v>8</v>
@@ -5920,9 +6644,8 @@
       <c r="D232" t="s">
         <v>350</v>
       </c>
-      <c r="E232" s="6" t="str" cm="1">
-        <f t="array" ref="E232">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>26-09-2026 21:05</v>
+      <c r="E232" s="6" t="s">
+        <v>621</v>
       </c>
       <c r="F232" s="4" t="s">
         <v>8</v>
@@ -5938,9 +6661,8 @@
       <c r="D233" t="s">
         <v>350</v>
       </c>
-      <c r="E233" s="6" t="str" cm="1">
-        <f t="array" ref="E233">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-09-2026 03:05</v>
+      <c r="E233" s="6" t="s">
+        <v>622</v>
       </c>
       <c r="F233" s="4" t="s">
         <v>8</v>
@@ -5956,9 +6678,8 @@
       <c r="D234" t="s">
         <v>350</v>
       </c>
-      <c r="E234" s="6" t="str" cm="1">
-        <f t="array" ref="E234">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-09-2026 06:05</v>
+      <c r="E234" s="6" t="s">
+        <v>623</v>
       </c>
       <c r="F234" s="4" t="s">
         <v>8</v>
@@ -5974,9 +6695,8 @@
       <c r="D235" t="s">
         <v>350</v>
       </c>
-      <c r="E235" s="6" t="str" cm="1">
-        <f t="array" ref="E235">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-09-2026 08:35</v>
+      <c r="E235" s="6" t="s">
+        <v>624</v>
       </c>
       <c r="F235" s="4" t="s">
         <v>8</v>
@@ -5992,9 +6712,8 @@
       <c r="D236" t="s">
         <v>350</v>
       </c>
-      <c r="E236" s="6" t="str" cm="1">
-        <f t="array" ref="E236">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-09-2026 11:35</v>
+      <c r="E236" s="6" t="s">
+        <v>625</v>
       </c>
       <c r="F236" s="4" t="s">
         <v>8</v>
@@ -6010,9 +6729,8 @@
       <c r="D237" t="s">
         <v>350</v>
       </c>
-      <c r="E237" s="6" t="str" cm="1">
-        <f t="array" ref="E237">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-09-2026 17:35</v>
+      <c r="E237" s="6" t="s">
+        <v>626</v>
       </c>
       <c r="F237" s="4" t="s">
         <v>8</v>
@@ -6028,9 +6746,8 @@
       <c r="D238" t="s">
         <v>350</v>
       </c>
-      <c r="E238" s="6" t="str" cm="1">
-        <f t="array" ref="E238">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-09-2026 19:05</v>
+      <c r="E238" s="6" t="s">
+        <v>627</v>
       </c>
       <c r="F238" s="4" t="s">
         <v>8</v>
@@ -6046,9 +6763,8 @@
       <c r="D239" t="s">
         <v>350</v>
       </c>
-      <c r="E239" s="6" t="str" cm="1">
-        <f t="array" ref="E239">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>27-09-2026 21:05</v>
+      <c r="E239" s="6" t="s">
+        <v>628</v>
       </c>
       <c r="F239" s="4" t="s">
         <v>8</v>
@@ -6064,9 +6780,8 @@
       <c r="D240" t="s">
         <v>350</v>
       </c>
-      <c r="E240" s="6" t="str" cm="1">
-        <f t="array" ref="E240">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-09-2026 03:05</v>
+      <c r="E240" s="6" t="s">
+        <v>629</v>
       </c>
       <c r="F240" s="4" t="s">
         <v>8</v>
@@ -6082,9 +6797,8 @@
       <c r="D241" t="s">
         <v>350</v>
       </c>
-      <c r="E241" s="6" t="str" cm="1">
-        <f t="array" ref="E241">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-09-2026 06:05</v>
+      <c r="E241" s="6" t="s">
+        <v>630</v>
       </c>
       <c r="F241" s="4" t="s">
         <v>8</v>
@@ -6100,9 +6814,8 @@
       <c r="D242" t="s">
         <v>350</v>
       </c>
-      <c r="E242" s="6" t="str" cm="1">
-        <f t="array" ref="E242">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-09-2026 08:35</v>
+      <c r="E242" s="6" t="s">
+        <v>631</v>
       </c>
       <c r="F242" s="4" t="s">
         <v>8</v>
@@ -6118,9 +6831,8 @@
       <c r="D243" t="s">
         <v>350</v>
       </c>
-      <c r="E243" s="6" t="str" cm="1">
-        <f t="array" ref="E243">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-09-2026 11:35</v>
+      <c r="E243" s="6" t="s">
+        <v>632</v>
       </c>
       <c r="F243" s="4" t="s">
         <v>8</v>
@@ -6136,9 +6848,8 @@
       <c r="D244" t="s">
         <v>350</v>
       </c>
-      <c r="E244" s="6" t="str" cm="1">
-        <f t="array" ref="E244">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-09-2026 17:35</v>
+      <c r="E244" s="6" t="s">
+        <v>633</v>
       </c>
       <c r="F244" s="4" t="s">
         <v>8</v>
@@ -6154,9 +6865,8 @@
       <c r="D245" t="s">
         <v>350</v>
       </c>
-      <c r="E245" s="6" t="str" cm="1">
-        <f t="array" ref="E245">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-09-2026 19:05</v>
+      <c r="E245" s="6" t="s">
+        <v>634</v>
       </c>
       <c r="F245" s="4" t="s">
         <v>8</v>
@@ -6172,9 +6882,8 @@
       <c r="D246" t="s">
         <v>350</v>
       </c>
-      <c r="E246" s="6" t="str" cm="1">
-        <f t="array" ref="E246">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>28-09-2026 21:05</v>
+      <c r="E246" s="6" t="s">
+        <v>635</v>
       </c>
       <c r="F246" s="4" t="s">
         <v>8</v>
@@ -6190,9 +6899,8 @@
       <c r="D247" t="s">
         <v>350</v>
       </c>
-      <c r="E247" s="6" t="str" cm="1">
-        <f t="array" ref="E247">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-09-2026 03:05</v>
+      <c r="E247" s="6" t="s">
+        <v>636</v>
       </c>
       <c r="F247" s="4" t="s">
         <v>8</v>
@@ -6208,9 +6916,8 @@
       <c r="D248" t="s">
         <v>350</v>
       </c>
-      <c r="E248" s="6" t="str" cm="1">
-        <f t="array" ref="E248">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-09-2026 06:05</v>
+      <c r="E248" s="6" t="s">
+        <v>637</v>
       </c>
       <c r="F248" s="4" t="s">
         <v>8</v>
@@ -6226,9 +6933,8 @@
       <c r="D249" t="s">
         <v>350</v>
       </c>
-      <c r="E249" s="6" t="str" cm="1">
-        <f t="array" ref="E249">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-09-2026 08:35</v>
+      <c r="E249" s="6" t="s">
+        <v>638</v>
       </c>
       <c r="F249" s="4" t="s">
         <v>8</v>
@@ -6244,9 +6950,8 @@
       <c r="D250" t="s">
         <v>350</v>
       </c>
-      <c r="E250" s="6" t="str" cm="1">
-        <f t="array" ref="E250">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-09-2026 11:35</v>
+      <c r="E250" s="6" t="s">
+        <v>639</v>
       </c>
       <c r="F250" s="4" t="s">
         <v>8</v>
@@ -6262,9 +6967,8 @@
       <c r="D251" t="s">
         <v>350</v>
       </c>
-      <c r="E251" s="6" t="str" cm="1">
-        <f t="array" ref="E251">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-09-2026 17:35</v>
+      <c r="E251" s="6" t="s">
+        <v>640</v>
       </c>
       <c r="F251" s="4" t="s">
         <v>8</v>
@@ -6280,9 +6984,8 @@
       <c r="D252" t="s">
         <v>350</v>
       </c>
-      <c r="E252" s="6" t="str" cm="1">
-        <f t="array" ref="E252">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-09-2026 19:05</v>
+      <c r="E252" s="6" t="s">
+        <v>641</v>
       </c>
       <c r="F252" s="4" t="s">
         <v>8</v>
@@ -6298,9 +7001,8 @@
       <c r="D253" t="s">
         <v>350</v>
       </c>
-      <c r="E253" s="6" t="str" cm="1">
-        <f t="array" ref="E253">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>29-09-2026 21:05</v>
+      <c r="E253" s="6" t="s">
+        <v>642</v>
       </c>
       <c r="F253" s="4" t="s">
         <v>8</v>
@@ -6316,9 +7018,8 @@
       <c r="D254" t="s">
         <v>350</v>
       </c>
-      <c r="E254" s="6" t="str" cm="1">
-        <f t="array" ref="E254">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-09-2026 03:05</v>
+      <c r="E254" s="6" t="s">
+        <v>643</v>
       </c>
       <c r="F254" s="4" t="s">
         <v>8</v>
@@ -6334,9 +7035,8 @@
       <c r="D255" t="s">
         <v>350</v>
       </c>
-      <c r="E255" s="6" t="str" cm="1">
-        <f t="array" ref="E255">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-09-2026 06:05</v>
+      <c r="E255" s="6" t="s">
+        <v>644</v>
       </c>
       <c r="F255" s="4" t="s">
         <v>8</v>
@@ -6352,9 +7052,8 @@
       <c r="D256" t="s">
         <v>350</v>
       </c>
-      <c r="E256" s="6" t="str" cm="1">
-        <f t="array" ref="E256">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-09-2026 08:35</v>
+      <c r="E256" s="6" t="s">
+        <v>645</v>
       </c>
       <c r="F256" s="4" t="s">
         <v>8</v>
@@ -6370,9 +7069,8 @@
       <c r="D257" t="s">
         <v>350</v>
       </c>
-      <c r="E257" s="6" t="str" cm="1">
-        <f t="array" ref="E257">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-09-2026 11:35</v>
+      <c r="E257" s="6" t="s">
+        <v>646</v>
       </c>
       <c r="F257" s="4" t="s">
         <v>8</v>
@@ -6388,9 +7086,8 @@
       <c r="D258" t="s">
         <v>350</v>
       </c>
-      <c r="E258" s="6" t="str" cm="1">
-        <f t="array" ref="E258">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-09-2026 17:35</v>
+      <c r="E258" s="6" t="s">
+        <v>647</v>
       </c>
       <c r="F258" s="4" t="s">
         <v>8</v>
@@ -6406,9 +7103,8 @@
       <c r="D259" t="s">
         <v>350</v>
       </c>
-      <c r="E259" s="6" t="str" cm="1">
-        <f t="array" ref="E259">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-09-2026 19:05</v>
+      <c r="E259" s="6" t="s">
+        <v>648</v>
       </c>
       <c r="F259" s="4" t="s">
         <v>8</v>
@@ -6424,9 +7120,8 @@
       <c r="D260" t="s">
         <v>350</v>
       </c>
-      <c r="E260" s="6" t="str" cm="1">
-        <f t="array" ref="E260">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>30-09-2026 21:05</v>
+      <c r="E260" s="6" t="s">
+        <v>649</v>
       </c>
       <c r="F260" s="4" t="s">
         <v>8</v>
@@ -6442,9 +7137,8 @@
       <c r="D261" t="s">
         <v>350</v>
       </c>
-      <c r="E261" s="6" t="str" cm="1">
-        <f t="array" ref="E261">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-10-2026 03:05</v>
+      <c r="E261" s="6" t="s">
+        <v>650</v>
       </c>
       <c r="F261" s="4" t="s">
         <v>8</v>
@@ -6460,9 +7154,8 @@
       <c r="D262" t="s">
         <v>350</v>
       </c>
-      <c r="E262" s="6" t="str" cm="1">
-        <f t="array" ref="E262">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-10-2026 06:05</v>
+      <c r="E262" s="6" t="s">
+        <v>651</v>
       </c>
       <c r="F262" s="4" t="s">
         <v>8</v>
@@ -6478,9 +7171,8 @@
       <c r="D263" t="s">
         <v>350</v>
       </c>
-      <c r="E263" s="6" t="str" cm="1">
-        <f t="array" ref="E263">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-10-2026 08:35</v>
+      <c r="E263" s="6" t="s">
+        <v>652</v>
       </c>
       <c r="F263" s="4" t="s">
         <v>8</v>
@@ -6496,9 +7188,8 @@
       <c r="D264" t="s">
         <v>350</v>
       </c>
-      <c r="E264" s="6" t="str" cm="1">
-        <f t="array" ref="E264">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-10-2026 11:35</v>
+      <c r="E264" s="6" t="s">
+        <v>653</v>
       </c>
       <c r="F264" s="4" t="s">
         <v>8</v>
@@ -6514,9 +7205,8 @@
       <c r="D265" t="s">
         <v>350</v>
       </c>
-      <c r="E265" s="6" t="str" cm="1">
-        <f t="array" ref="E265">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-10-2026 17:35</v>
+      <c r="E265" s="6" t="s">
+        <v>654</v>
       </c>
       <c r="F265" s="4" t="s">
         <v>8</v>
@@ -6532,9 +7222,8 @@
       <c r="D266" t="s">
         <v>350</v>
       </c>
-      <c r="E266" s="6" t="str" cm="1">
-        <f t="array" ref="E266">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-10-2026 19:05</v>
+      <c r="E266" s="6" t="s">
+        <v>655</v>
       </c>
       <c r="F266" s="4" t="s">
         <v>8</v>
@@ -6550,9 +7239,8 @@
       <c r="D267" t="s">
         <v>350</v>
       </c>
-      <c r="E267" s="6" t="str" cm="1">
-        <f t="array" ref="E267">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>01-10-2026 21:05</v>
+      <c r="E267" s="6" t="s">
+        <v>656</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>8</v>
@@ -6568,9 +7256,8 @@
       <c r="D268" t="s">
         <v>350</v>
       </c>
-      <c r="E268" s="6" t="str" cm="1">
-        <f t="array" ref="E268">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-10-2026 03:05</v>
+      <c r="E268" s="6" t="s">
+        <v>657</v>
       </c>
       <c r="F268" s="4" t="s">
         <v>8</v>
@@ -6586,9 +7273,8 @@
       <c r="D269" t="s">
         <v>350</v>
       </c>
-      <c r="E269" s="6" t="str" cm="1">
-        <f t="array" ref="E269">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-10-2026 06:05</v>
+      <c r="E269" s="6" t="s">
+        <v>658</v>
       </c>
       <c r="F269" s="4" t="s">
         <v>8</v>
@@ -6604,9 +7290,8 @@
       <c r="D270" t="s">
         <v>351</v>
       </c>
-      <c r="E270" s="6" t="str" cm="1">
-        <f t="array" ref="E270">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-10-2026 08:35</v>
+      <c r="E270" s="6" t="s">
+        <v>659</v>
       </c>
       <c r="F270" s="4" t="s">
         <v>8</v>
@@ -6622,9 +7307,8 @@
       <c r="D271" t="s">
         <v>351</v>
       </c>
-      <c r="E271" s="6" t="str" cm="1">
-        <f t="array" ref="E271">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-10-2026 11:35</v>
+      <c r="E271" s="6" t="s">
+        <v>660</v>
       </c>
       <c r="F271" s="4" t="s">
         <v>8</v>
@@ -6640,9 +7324,8 @@
       <c r="D272" t="s">
         <v>351</v>
       </c>
-      <c r="E272" s="6" t="str" cm="1">
-        <f t="array" ref="E272">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-10-2026 17:35</v>
+      <c r="E272" s="6" t="s">
+        <v>661</v>
       </c>
       <c r="F272" s="4" t="s">
         <v>8</v>
@@ -6658,9 +7341,8 @@
       <c r="D273" t="s">
         <v>351</v>
       </c>
-      <c r="E273" s="6" t="str" cm="1">
-        <f t="array" ref="E273">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-10-2026 19:05</v>
+      <c r="E273" s="6" t="s">
+        <v>662</v>
       </c>
       <c r="F273" s="4" t="s">
         <v>8</v>
@@ -6676,9 +7358,8 @@
       <c r="D274" t="s">
         <v>351</v>
       </c>
-      <c r="E274" s="6" t="str" cm="1">
-        <f t="array" ref="E274">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>02-10-2026 21:05</v>
+      <c r="E274" s="6" t="s">
+        <v>663</v>
       </c>
       <c r="F274" s="4" t="s">
         <v>8</v>
@@ -6694,9 +7375,8 @@
       <c r="D275" t="s">
         <v>351</v>
       </c>
-      <c r="E275" s="6" t="str" cm="1">
-        <f t="array" ref="E275">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-10-2026 03:05</v>
+      <c r="E275" s="6" t="s">
+        <v>664</v>
       </c>
       <c r="F275" s="4" t="s">
         <v>8</v>
@@ -6712,9 +7392,8 @@
       <c r="D276" t="s">
         <v>351</v>
       </c>
-      <c r="E276" s="6" t="str" cm="1">
-        <f t="array" ref="E276">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-10-2026 06:05</v>
+      <c r="E276" s="6" t="s">
+        <v>665</v>
       </c>
       <c r="F276" s="4" t="s">
         <v>8</v>
@@ -6730,9 +7409,8 @@
       <c r="D277" t="s">
         <v>351</v>
       </c>
-      <c r="E277" s="6" t="str" cm="1">
-        <f t="array" ref="E277">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-10-2026 08:35</v>
+      <c r="E277" s="6" t="s">
+        <v>666</v>
       </c>
       <c r="F277" s="4" t="s">
         <v>8</v>
@@ -6748,9 +7426,8 @@
       <c r="D278" t="s">
         <v>351</v>
       </c>
-      <c r="E278" s="6" t="str" cm="1">
-        <f t="array" ref="E278">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-10-2026 11:35</v>
+      <c r="E278" s="6" t="s">
+        <v>667</v>
       </c>
       <c r="F278" s="4" t="s">
         <v>8</v>
@@ -6766,9 +7443,8 @@
       <c r="D279" t="s">
         <v>351</v>
       </c>
-      <c r="E279" s="6" t="str" cm="1">
-        <f t="array" ref="E279">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-10-2026 17:35</v>
+      <c r="E279" s="6" t="s">
+        <v>668</v>
       </c>
       <c r="F279" s="4" t="s">
         <v>8</v>
@@ -6784,9 +7460,8 @@
       <c r="D280" t="s">
         <v>351</v>
       </c>
-      <c r="E280" s="6" t="str" cm="1">
-        <f t="array" ref="E280">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-10-2026 19:05</v>
+      <c r="E280" s="6" t="s">
+        <v>669</v>
       </c>
       <c r="F280" s="4" t="s">
         <v>8</v>
@@ -6802,9 +7477,8 @@
       <c r="D281" t="s">
         <v>351</v>
       </c>
-      <c r="E281" s="6" t="str" cm="1">
-        <f t="array" ref="E281">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>03-10-2026 21:05</v>
+      <c r="E281" s="6" t="s">
+        <v>670</v>
       </c>
       <c r="F281" s="4" t="s">
         <v>8</v>
@@ -6820,9 +7494,8 @@
       <c r="D282" t="s">
         <v>351</v>
       </c>
-      <c r="E282" s="6" t="str" cm="1">
-        <f t="array" ref="E282">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-10-2026 03:05</v>
+      <c r="E282" s="6" t="s">
+        <v>671</v>
       </c>
       <c r="F282" s="4" t="s">
         <v>8</v>
@@ -6838,9 +7511,8 @@
       <c r="D283" t="s">
         <v>351</v>
       </c>
-      <c r="E283" s="6" t="str" cm="1">
-        <f t="array" ref="E283">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-10-2026 06:05</v>
+      <c r="E283" s="6" t="s">
+        <v>672</v>
       </c>
       <c r="F283" s="4" t="s">
         <v>8</v>
@@ -6856,9 +7528,8 @@
       <c r="D284" t="s">
         <v>351</v>
       </c>
-      <c r="E284" s="6" t="str" cm="1">
-        <f t="array" ref="E284">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-10-2026 08:35</v>
+      <c r="E284" s="6" t="s">
+        <v>673</v>
       </c>
       <c r="F284" s="4" t="s">
         <v>8</v>
@@ -6874,9 +7545,8 @@
       <c r="D285" t="s">
         <v>351</v>
       </c>
-      <c r="E285" s="6" t="str" cm="1">
-        <f t="array" ref="E285">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-10-2026 11:35</v>
+      <c r="E285" s="6" t="s">
+        <v>674</v>
       </c>
       <c r="F285" s="4" t="s">
         <v>8</v>
@@ -6892,9 +7562,8 @@
       <c r="D286" t="s">
         <v>351</v>
       </c>
-      <c r="E286" s="6" t="str" cm="1">
-        <f t="array" ref="E286">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-10-2026 17:35</v>
+      <c r="E286" s="6" t="s">
+        <v>675</v>
       </c>
       <c r="F286" s="4" t="s">
         <v>8</v>
@@ -6910,9 +7579,8 @@
       <c r="D287" t="s">
         <v>351</v>
       </c>
-      <c r="E287" s="6" t="str" cm="1">
-        <f t="array" ref="E287">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-10-2026 19:05</v>
+      <c r="E287" s="6" t="s">
+        <v>676</v>
       </c>
       <c r="F287" s="4" t="s">
         <v>8</v>
@@ -6928,9 +7596,8 @@
       <c r="D288" t="s">
         <v>351</v>
       </c>
-      <c r="E288" s="6" t="str" cm="1">
-        <f t="array" ref="E288">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>04-10-2026 21:05</v>
+      <c r="E288" s="6" t="s">
+        <v>677</v>
       </c>
       <c r="F288" s="4" t="s">
         <v>8</v>
@@ -6946,9 +7613,8 @@
       <c r="D289" t="s">
         <v>351</v>
       </c>
-      <c r="E289" s="6" t="str" cm="1">
-        <f t="array" ref="E289">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-10-2026 03:05</v>
+      <c r="E289" s="6" t="s">
+        <v>678</v>
       </c>
       <c r="F289" s="4" t="s">
         <v>8</v>
@@ -6964,9 +7630,8 @@
       <c r="D290" t="s">
         <v>351</v>
       </c>
-      <c r="E290" s="6" t="str" cm="1">
-        <f t="array" ref="E290">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-10-2026 06:05</v>
+      <c r="E290" s="6" t="s">
+        <v>679</v>
       </c>
       <c r="F290" s="4" t="s">
         <v>8</v>
@@ -6982,9 +7647,8 @@
       <c r="D291" t="s">
         <v>351</v>
       </c>
-      <c r="E291" s="6" t="str" cm="1">
-        <f t="array" ref="E291">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-10-2026 08:35</v>
+      <c r="E291" s="6" t="s">
+        <v>680</v>
       </c>
       <c r="F291" s="4" t="s">
         <v>8</v>
@@ -7000,9 +7664,8 @@
       <c r="D292" t="s">
         <v>351</v>
       </c>
-      <c r="E292" s="6" t="str" cm="1">
-        <f t="array" ref="E292">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-10-2026 11:35</v>
+      <c r="E292" s="6" t="s">
+        <v>681</v>
       </c>
       <c r="F292" s="4" t="s">
         <v>8</v>
@@ -7018,9 +7681,8 @@
       <c r="D293" t="s">
         <v>351</v>
       </c>
-      <c r="E293" s="6" t="str" cm="1">
-        <f t="array" ref="E293">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-10-2026 17:35</v>
+      <c r="E293" s="6" t="s">
+        <v>682</v>
       </c>
       <c r="F293" s="4" t="s">
         <v>8</v>
@@ -7036,9 +7698,8 @@
       <c r="D294" t="s">
         <v>351</v>
       </c>
-      <c r="E294" s="6" t="str" cm="1">
-        <f t="array" ref="E294">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-10-2026 19:05</v>
+      <c r="E294" s="6" t="s">
+        <v>683</v>
       </c>
       <c r="F294" s="4" t="s">
         <v>8</v>
@@ -7054,9 +7715,8 @@
       <c r="D295" t="s">
         <v>351</v>
       </c>
-      <c r="E295" s="6" t="str" cm="1">
-        <f t="array" ref="E295">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>05-10-2026 21:05</v>
+      <c r="E295" s="6" t="s">
+        <v>684</v>
       </c>
       <c r="F295" s="4" t="s">
         <v>8</v>
@@ -7072,9 +7732,8 @@
       <c r="D296" t="s">
         <v>351</v>
       </c>
-      <c r="E296" s="6" t="str" cm="1">
-        <f t="array" ref="E296">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-10-2026 03:05</v>
+      <c r="E296" s="6" t="s">
+        <v>685</v>
       </c>
       <c r="F296" s="4" t="s">
         <v>8</v>
@@ -7090,9 +7749,8 @@
       <c r="D297" t="s">
         <v>351</v>
       </c>
-      <c r="E297" s="6" t="str" cm="1">
-        <f t="array" ref="E297">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-10-2026 06:05</v>
+      <c r="E297" s="6" t="s">
+        <v>686</v>
       </c>
       <c r="F297" s="4" t="s">
         <v>8</v>
@@ -7108,9 +7766,8 @@
       <c r="D298" t="s">
         <v>351</v>
       </c>
-      <c r="E298" s="6" t="str" cm="1">
-        <f t="array" ref="E298">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-10-2026 08:35</v>
+      <c r="E298" s="6" t="s">
+        <v>687</v>
       </c>
       <c r="F298" s="4" t="s">
         <v>8</v>
@@ -7126,9 +7783,8 @@
       <c r="D299" t="s">
         <v>351</v>
       </c>
-      <c r="E299" s="6" t="str" cm="1">
-        <f t="array" ref="E299">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-10-2026 11:35</v>
+      <c r="E299" s="6" t="s">
+        <v>688</v>
       </c>
       <c r="F299" s="4" t="s">
         <v>8</v>
@@ -7144,9 +7800,8 @@
       <c r="D300" t="s">
         <v>351</v>
       </c>
-      <c r="E300" s="6" t="str" cm="1">
-        <f t="array" ref="E300">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-10-2026 17:35</v>
+      <c r="E300" s="6" t="s">
+        <v>689</v>
       </c>
       <c r="F300" s="4" t="s">
         <v>8</v>
@@ -7162,9 +7817,8 @@
       <c r="D301" t="s">
         <v>351</v>
       </c>
-      <c r="E301" s="6" t="str" cm="1">
-        <f t="array" ref="E301">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-10-2026 19:05</v>
+      <c r="E301" s="6" t="s">
+        <v>690</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>8</v>
@@ -7180,9 +7834,8 @@
       <c r="D302" t="s">
         <v>351</v>
       </c>
-      <c r="E302" s="6" t="str" cm="1">
-        <f t="array" ref="E302">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>06-10-2026 21:05</v>
+      <c r="E302" s="6" t="s">
+        <v>691</v>
       </c>
       <c r="F302" s="4" t="s">
         <v>8</v>
@@ -7198,9 +7851,8 @@
       <c r="D303" t="s">
         <v>351</v>
       </c>
-      <c r="E303" s="6" t="str" cm="1">
-        <f t="array" ref="E303">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-10-2026 03:05</v>
+      <c r="E303" s="6" t="s">
+        <v>692</v>
       </c>
       <c r="F303" s="4" t="s">
         <v>8</v>
@@ -7216,9 +7868,8 @@
       <c r="D304" t="s">
         <v>351</v>
       </c>
-      <c r="E304" s="6" t="str" cm="1">
-        <f t="array" ref="E304">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-10-2026 06:05</v>
+      <c r="E304" s="6" t="s">
+        <v>693</v>
       </c>
       <c r="F304" s="4" t="s">
         <v>8</v>
@@ -7234,9 +7885,8 @@
       <c r="D305" t="s">
         <v>351</v>
       </c>
-      <c r="E305" s="6" t="str" cm="1">
-        <f t="array" ref="E305">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-10-2026 08:35</v>
+      <c r="E305" s="6" t="s">
+        <v>694</v>
       </c>
       <c r="F305" s="4" t="s">
         <v>8</v>
@@ -7252,9 +7902,8 @@
       <c r="D306" t="s">
         <v>351</v>
       </c>
-      <c r="E306" s="6" t="str" cm="1">
-        <f t="array" ref="E306">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-10-2026 11:35</v>
+      <c r="E306" s="6" t="s">
+        <v>695</v>
       </c>
       <c r="F306" s="4" t="s">
         <v>8</v>
@@ -7270,9 +7919,8 @@
       <c r="D307" t="s">
         <v>351</v>
       </c>
-      <c r="E307" s="6" t="str" cm="1">
-        <f t="array" ref="E307">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-10-2026 17:35</v>
+      <c r="E307" s="6" t="s">
+        <v>696</v>
       </c>
       <c r="F307" s="4" t="s">
         <v>8</v>
@@ -7288,9 +7936,8 @@
       <c r="D308" t="s">
         <v>351</v>
       </c>
-      <c r="E308" s="6" t="str" cm="1">
-        <f t="array" ref="E308">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-10-2026 19:05</v>
+      <c r="E308" s="6" t="s">
+        <v>697</v>
       </c>
       <c r="F308" s="4" t="s">
         <v>8</v>
@@ -7306,9 +7953,8 @@
       <c r="D309" t="s">
         <v>351</v>
       </c>
-      <c r="E309" s="6" t="str" cm="1">
-        <f t="array" ref="E309">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>07-10-2026 21:05</v>
+      <c r="E309" s="6" t="s">
+        <v>698</v>
       </c>
       <c r="F309" s="4" t="s">
         <v>8</v>
@@ -7324,9 +7970,8 @@
       <c r="D310" t="s">
         <v>351</v>
       </c>
-      <c r="E310" s="6" t="str" cm="1">
-        <f t="array" ref="E310">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-10-2026 03:05</v>
+      <c r="E310" s="6" t="s">
+        <v>699</v>
       </c>
       <c r="F310" s="4" t="s">
         <v>8</v>
@@ -7342,9 +7987,8 @@
       <c r="D311" t="s">
         <v>351</v>
       </c>
-      <c r="E311" s="6" t="str" cm="1">
-        <f t="array" ref="E311">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-10-2026 06:05</v>
+      <c r="E311" s="6" t="s">
+        <v>700</v>
       </c>
       <c r="F311" s="4" t="s">
         <v>8</v>
@@ -7360,9 +8004,8 @@
       <c r="D312" t="s">
         <v>351</v>
       </c>
-      <c r="E312" s="6" t="str" cm="1">
-        <f t="array" ref="E312">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-10-2026 08:35</v>
+      <c r="E312" s="6" t="s">
+        <v>701</v>
       </c>
       <c r="F312" s="4" t="s">
         <v>8</v>
@@ -7378,9 +8021,8 @@
       <c r="D313" t="s">
         <v>351</v>
       </c>
-      <c r="E313" s="6" t="str" cm="1">
-        <f t="array" ref="E313">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-10-2026 11:35</v>
+      <c r="E313" s="6" t="s">
+        <v>702</v>
       </c>
       <c r="F313" s="4" t="s">
         <v>8</v>
@@ -7396,9 +8038,8 @@
       <c r="D314" t="s">
         <v>351</v>
       </c>
-      <c r="E314" s="6" t="str" cm="1">
-        <f t="array" ref="E314">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-10-2026 17:35</v>
+      <c r="E314" s="6" t="s">
+        <v>703</v>
       </c>
       <c r="F314" s="4" t="s">
         <v>8</v>
@@ -7414,9 +8055,8 @@
       <c r="D315" t="s">
         <v>351</v>
       </c>
-      <c r="E315" s="6" t="str" cm="1">
-        <f t="array" ref="E315">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-10-2026 19:05</v>
+      <c r="E315" s="6" t="s">
+        <v>704</v>
       </c>
       <c r="F315" s="4" t="s">
         <v>8</v>
@@ -7432,9 +8072,8 @@
       <c r="D316" t="s">
         <v>351</v>
       </c>
-      <c r="E316" s="6" t="str" cm="1">
-        <f t="array" ref="E316">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>08-10-2026 21:05</v>
+      <c r="E316" s="6" t="s">
+        <v>705</v>
       </c>
       <c r="F316" s="4" t="s">
         <v>8</v>
@@ -7450,9 +8089,8 @@
       <c r="D317" t="s">
         <v>351</v>
       </c>
-      <c r="E317" s="6" t="str" cm="1">
-        <f t="array" ref="E317">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-10-2026 03:05</v>
+      <c r="E317" s="6" t="s">
+        <v>706</v>
       </c>
       <c r="F317" s="4" t="s">
         <v>8</v>
@@ -7468,9 +8106,8 @@
       <c r="D318" t="s">
         <v>351</v>
       </c>
-      <c r="E318" s="6" t="str" cm="1">
-        <f t="array" ref="E318">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-10-2026 06:05</v>
+      <c r="E318" s="6" t="s">
+        <v>707</v>
       </c>
       <c r="F318" s="4" t="s">
         <v>8</v>
@@ -7486,9 +8123,8 @@
       <c r="D319" t="s">
         <v>351</v>
       </c>
-      <c r="E319" s="6" t="str" cm="1">
-        <f t="array" ref="E319">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-10-2026 08:35</v>
+      <c r="E319" s="6" t="s">
+        <v>708</v>
       </c>
       <c r="F319" s="4" t="s">
         <v>8</v>
@@ -7504,9 +8140,8 @@
       <c r="D320" t="s">
         <v>351</v>
       </c>
-      <c r="E320" s="6" t="str" cm="1">
-        <f t="array" ref="E320">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-10-2026 11:35</v>
+      <c r="E320" s="6" t="s">
+        <v>709</v>
       </c>
       <c r="F320" s="4" t="s">
         <v>8</v>
@@ -7522,9 +8157,8 @@
       <c r="D321" t="s">
         <v>352</v>
       </c>
-      <c r="E321" s="6" t="str" cm="1">
-        <f t="array" ref="E321">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-10-2026 17:35</v>
+      <c r="E321" s="6" t="s">
+        <v>710</v>
       </c>
       <c r="F321" s="4" t="s">
         <v>8</v>
@@ -7540,9 +8174,8 @@
       <c r="D322" t="s">
         <v>352</v>
       </c>
-      <c r="E322" s="6" t="str" cm="1">
-        <f t="array" ref="E322">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-10-2026 19:05</v>
+      <c r="E322" s="6" t="s">
+        <v>711</v>
       </c>
       <c r="F322" s="4" t="s">
         <v>8</v>
@@ -7558,9 +8191,8 @@
       <c r="D323" t="s">
         <v>352</v>
       </c>
-      <c r="E323" s="6" t="str" cm="1">
-        <f t="array" ref="E323">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>09-10-2026 21:05</v>
+      <c r="E323" s="6" t="s">
+        <v>712</v>
       </c>
       <c r="F323" s="4" t="s">
         <v>8</v>
@@ -7576,9 +8208,8 @@
       <c r="D324" t="s">
         <v>352</v>
       </c>
-      <c r="E324" s="6" t="str" cm="1">
-        <f t="array" ref="E324">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-10-2026 03:05</v>
+      <c r="E324" s="6" t="s">
+        <v>713</v>
       </c>
       <c r="F324" s="4" t="s">
         <v>8</v>
@@ -7594,9 +8225,8 @@
       <c r="D325" t="s">
         <v>352</v>
       </c>
-      <c r="E325" s="6" t="str" cm="1">
-        <f t="array" ref="E325">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-10-2026 06:05</v>
+      <c r="E325" s="6" t="s">
+        <v>714</v>
       </c>
       <c r="F325" s="4" t="s">
         <v>8</v>
@@ -7612,9 +8242,8 @@
       <c r="D326" t="s">
         <v>352</v>
       </c>
-      <c r="E326" s="6" t="str" cm="1">
-        <f t="array" ref="E326">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-10-2026 08:35</v>
+      <c r="E326" s="6" t="s">
+        <v>715</v>
       </c>
       <c r="F326" s="4" t="s">
         <v>8</v>
@@ -7630,9 +8259,8 @@
       <c r="D327" t="s">
         <v>352</v>
       </c>
-      <c r="E327" s="6" t="str" cm="1">
-        <f t="array" ref="E327">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-10-2026 11:35</v>
+      <c r="E327" s="6" t="s">
+        <v>716</v>
       </c>
       <c r="F327" s="4" t="s">
         <v>8</v>
@@ -7648,9 +8276,8 @@
       <c r="D328" t="s">
         <v>352</v>
       </c>
-      <c r="E328" s="6" t="str" cm="1">
-        <f t="array" ref="E328">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-10-2026 17:35</v>
+      <c r="E328" s="6" t="s">
+        <v>717</v>
       </c>
       <c r="F328" s="4" t="s">
         <v>8</v>
@@ -7666,9 +8293,8 @@
       <c r="D329" t="s">
         <v>352</v>
       </c>
-      <c r="E329" s="6" t="str" cm="1">
-        <f t="array" ref="E329">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-10-2026 19:05</v>
+      <c r="E329" s="6" t="s">
+        <v>718</v>
       </c>
       <c r="F329" s="4" t="s">
         <v>8</v>
@@ -7684,9 +8310,8 @@
       <c r="D330" t="s">
         <v>352</v>
       </c>
-      <c r="E330" s="6" t="str" cm="1">
-        <f t="array" ref="E330">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>10-10-2026 21:05</v>
+      <c r="E330" s="6" t="s">
+        <v>719</v>
       </c>
       <c r="F330" s="4" t="s">
         <v>8</v>
@@ -7702,9 +8327,8 @@
       <c r="D331" t="s">
         <v>352</v>
       </c>
-      <c r="E331" s="6" t="str" cm="1">
-        <f t="array" ref="E331">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>11-10-2026 03:05</v>
+      <c r="E331" s="6" t="s">
+        <v>720</v>
       </c>
       <c r="F331" s="4" t="s">
         <v>8</v>
@@ -7720,9 +8344,8 @@
       <c r="D332" t="s">
         <v>352</v>
       </c>
-      <c r="E332" s="6" t="str" cm="1">
-        <f t="array" ref="E332">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>11-10-2026 06:05</v>
+      <c r="E332" s="6" t="s">
+        <v>721</v>
       </c>
       <c r="F332" s="4" t="s">
         <v>8</v>
@@ -7738,9 +8361,8 @@
       <c r="D333" t="s">
         <v>352</v>
       </c>
-      <c r="E333" s="6" t="str" cm="1">
-        <f t="array" ref="E333">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>11-10-2026 08:35</v>
+      <c r="E333" s="6" t="s">
+        <v>722</v>
       </c>
       <c r="F333" s="4" t="s">
         <v>8</v>
@@ -7756,9 +8378,8 @@
       <c r="D334" t="s">
         <v>352</v>
       </c>
-      <c r="E334" s="6" t="str" cm="1">
-        <f t="array" ref="E334">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>11-10-2026 11:35</v>
+      <c r="E334" s="6" t="s">
+        <v>723</v>
       </c>
       <c r="F334" s="4" t="s">
         <v>8</v>
@@ -7774,9 +8395,8 @@
       <c r="D335" t="s">
         <v>352</v>
       </c>
-      <c r="E335" s="6" t="str" cm="1">
-        <f t="array" ref="E335">TEXT(DATE(2026,8,25)+INT((ROW()-2)/7),"DD-MM-YYYY")&amp;" "&amp;TEXT(INDEX($E$2:$E$8,MOD(ROW()-2,7)+1),"HH:MM")</f>
-        <v>11-10-2026 17:35</v>
+      <c r="E335" s="6" t="s">
+        <v>724</v>
       </c>
       <c r="F335" s="4" t="s">
         <v>8</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9633,9 +9633,14 @@
       <c r="E336" s="6" t="n">
         <v>46259.21180555555</v>
       </c>
-      <c r="F336" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F336" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>1087039570528816</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -659,9 +659,14 @@
       <c r="E3" s="6" t="n">
         <v>46259.25347222222</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1041011655496640</t>
         </is>
       </c>
     </row>
@@ -687,9 +692,14 @@
       <c r="E4" s="6" t="n">
         <v>46259.35763888889</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1681192342951285</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -722,9 +722,14 @@
       <c r="E5" s="6" t="n">
         <v>46259.48263888889</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1940562640241874</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -752,9 +752,14 @@
       <c r="E6" s="6" t="n">
         <v>46259.73263888889</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1742493296871639</t>
         </is>
       </c>
     </row>
@@ -777,9 +782,14 @@
       <c r="E7" s="6" t="n">
         <v>46259.79513888889</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1566193651965641</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -812,9 +812,14 @@
       <c r="E8" s="6" t="n">
         <v>46259.87847222222</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>27674179328950526</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanuk\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A319D0E-6970-495B-87DF-27114AF5D4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77980064-E30F-430D-89AC-2A7911C4125C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1742,7 +1742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I618"/>
+  <dimension ref="A1:H618"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3" customWidth="1"/>
@@ -1751,11 +1751,11 @@
     <col min="4" max="4" width="61.85546875" customWidth="1"/>
     <col min="5" max="5" width="29" style="8" customWidth="1"/>
     <col min="6" max="6" width="23.42578125" customWidth="1"/>
-    <col min="7" max="7" width="42.85546875" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="24.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1803,12 +1803,8 @@
       <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" t="b">
-        <f>ISNUMBER(E2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1830,12 +1826,8 @@
       <c r="G3" t="s">
         <v>14</v>
       </c>
-      <c r="I3" t="b">
-        <f t="shared" ref="I3:I24" si="0">ISNUMBER(E3)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1857,12 +1849,8 @@
       <c r="G4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>17</v>
       </c>
@@ -1881,12 +1869,8 @@
       <c r="G5" t="s">
         <v>18</v>
       </c>
-      <c r="I5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>19</v>
       </c>
@@ -1905,12 +1889,8 @@
       <c r="G6" t="s">
         <v>20</v>
       </c>
-      <c r="I6" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>21</v>
       </c>
@@ -1929,12 +1909,8 @@
       <c r="G7" t="s">
         <v>22</v>
       </c>
-      <c r="I7" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>23</v>
       </c>
@@ -1953,12 +1929,8 @@
       <c r="G8" t="s">
         <v>24</v>
       </c>
-      <c r="I8" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>25</v>
       </c>
@@ -1974,12 +1946,8 @@
       <c r="F9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I9" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>27</v>
       </c>
@@ -1995,12 +1963,8 @@
       <c r="F10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I10" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>28</v>
       </c>
@@ -2016,12 +1980,8 @@
       <c r="F11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I11" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>29</v>
       </c>
@@ -2037,12 +1997,8 @@
       <c r="F12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I12" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>30</v>
       </c>
@@ -2058,12 +2014,8 @@
       <c r="F13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I13" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>31</v>
       </c>
@@ -2079,12 +2031,8 @@
       <c r="F14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I14" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>32</v>
       </c>
@@ -2100,12 +2048,8 @@
       <c r="F15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I15" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>33</v>
       </c>
@@ -2116,17 +2060,13 @@
         <v>10</v>
       </c>
       <c r="E16" s="6">
-        <v>46261.128472222219</v>
+        <v>46307.795138888891</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I16" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>34</v>
       </c>
@@ -2137,17 +2077,13 @@
         <v>10</v>
       </c>
       <c r="E17" s="6">
-        <v>46261.253472222219</v>
+        <v>46307.878472222219</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I17" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>35</v>
       </c>
@@ -2158,17 +2094,13 @@
         <v>10</v>
       </c>
       <c r="E18" s="6">
-        <v>46261.357638888891</v>
+        <v>46308.128472222219</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I18" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>36</v>
       </c>
@@ -2179,17 +2111,13 @@
         <v>10</v>
       </c>
       <c r="E19" s="6">
-        <v>46261.482638888891</v>
+        <v>46308.253472222219</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I19" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>37</v>
       </c>
@@ -2200,17 +2128,13 @@
         <v>10</v>
       </c>
       <c r="E20" s="6">
-        <v>46261.732638888891</v>
+        <v>46308.357638888891</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I20" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>38</v>
       </c>
@@ -2221,17 +2145,13 @@
         <v>10</v>
       </c>
       <c r="E21" s="6">
-        <v>46261.795138888891</v>
+        <v>46308.482638888891</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I21" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>39</v>
       </c>
@@ -2242,17 +2162,13 @@
         <v>10</v>
       </c>
       <c r="E22" s="6">
-        <v>46261.878472222219</v>
+        <v>46262.010416666664</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I22" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>40</v>
       </c>
@@ -2268,12 +2184,8 @@
       <c r="F23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I23" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>41</v>
       </c>
@@ -2289,12 +2201,8 @@
       <c r="F24" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I24" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>42</v>
       </c>
@@ -2311,7 +2219,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>43</v>
       </c>
@@ -2328,7 +2236,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>44</v>
       </c>
@@ -2345,7 +2253,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>45</v>
       </c>
@@ -2362,7 +2270,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>46</v>
       </c>
@@ -2379,7 +2287,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>47</v>
       </c>
@@ -2396,7 +2304,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>48</v>
       </c>
@@ -2413,7 +2321,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>49</v>
       </c>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1211,9 +1211,14 @@
       <c r="E23" s="6" t="n">
         <v>46262.12847222222</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2229658101315834</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1241,9 +1241,14 @@
       <c r="E24" s="6" t="n">
         <v>46262.25347222222</v>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1059579046433701</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1271,9 +1271,14 @@
       <c r="E25" s="6" t="n">
         <v>46262.35763888889</v>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1767154904426467</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9081,9 +9081,14 @@
       <c r="E337" s="6" t="n">
         <v>46263.62847222222</v>
       </c>
-      <c r="F337" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F337" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>1090766826822757</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9111,9 +9111,14 @@
       <c r="E338" s="6" t="n">
         <v>46267.58680555555</v>
       </c>
-      <c r="F338" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F338" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>1095605719672201</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -9141,9 +9141,14 @@
       <c r="E339" s="6" t="n">
         <v>46272.21180555555</v>
       </c>
-      <c r="F339" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F339" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>1099483092617797</t>
         </is>
       </c>
     </row>
